--- a/109เปล่า.xlsx
+++ b/109เปล่า.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE864E60-448A-4BE2-AA3B-AEDA8083852F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857E5843-B452-47DD-90C3-4A77D6334CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{E3A30F9B-029D-4A93-B8CC-57CE95D4794C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3A30F9B-029D-4A93-B8CC-57CE95D4794C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="ก.ค. 69 หน้า 1 (2)" sheetId="2" r:id="rId2"/>
+    <sheet name="ก.ค. 69 หน้า 1 (2)" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -271,7 +270,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -325,13 +324,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="TH SarabunPSK"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="TH SarabunPSK"/>
@@ -341,27 +333,6 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="TH SarabunPSK"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF00B050"/>
-      <name val="TH SarabunPSK"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="TH SarabunPSK"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="3"/>
       <name val="TH SarabunPSK"/>
       <family val="2"/>
     </font>
@@ -433,6 +404,13 @@
       <name val="TH SarabunPSK"/>
       <family val="2"/>
       <charset val="222"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="TH SarabunPSK"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -577,7 +555,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -605,128 +583,145 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -743,79 +738,29 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2078,15 +2023,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C62D834A-4618-42D2-8FF5-87324A2D8919}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C10B2AA3-E05D-4804-9C45-423CCF1167CB}">
   <dimension ref="A1:AN54"/>
   <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="20.399999999999999"/>
@@ -2098,41 +2034,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="18" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="57"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="57"/>
-      <c r="V1" s="57"/>
-      <c r="W1" s="57"/>
-      <c r="X1" s="57"/>
-      <c r="Y1" s="57"/>
-      <c r="Z1" s="57"/>
-      <c r="AA1" s="57"/>
-      <c r="AB1" s="57"/>
-      <c r="AC1" s="57"/>
-      <c r="AD1" s="57"/>
-      <c r="AE1" s="57"/>
-      <c r="AF1" s="57"/>
-      <c r="AG1" s="57"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="55"/>
+      <c r="Q1" s="55"/>
+      <c r="R1" s="55"/>
+      <c r="S1" s="55"/>
+      <c r="T1" s="55"/>
+      <c r="U1" s="55"/>
+      <c r="V1" s="55"/>
+      <c r="W1" s="55"/>
+      <c r="X1" s="55"/>
+      <c r="Y1" s="55"/>
+      <c r="Z1" s="55"/>
+      <c r="AA1" s="55"/>
+      <c r="AB1" s="55"/>
+      <c r="AC1" s="55"/>
+      <c r="AD1" s="55"/>
+      <c r="AE1" s="55"/>
+      <c r="AF1" s="55"/>
+      <c r="AG1" s="55"/>
     </row>
     <row r="2" spans="1:33" ht="8.25" customHeight="1">
       <c r="A2" s="2"/>
@@ -2170,41 +2106,41 @@
       <c r="AG2" s="2"/>
     </row>
     <row r="3" spans="1:33" ht="24">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="13"/>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="13"/>
-      <c r="AB3" s="13"/>
-      <c r="AC3" s="13"/>
-      <c r="AD3" s="13"/>
-      <c r="AE3" s="13"/>
-      <c r="AF3" s="13"/>
-      <c r="AG3" s="13"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="56"/>
+      <c r="N3" s="56"/>
+      <c r="O3" s="56"/>
+      <c r="P3" s="56"/>
+      <c r="Q3" s="56"/>
+      <c r="R3" s="56"/>
+      <c r="S3" s="56"/>
+      <c r="T3" s="56"/>
+      <c r="U3" s="56"/>
+      <c r="V3" s="56"/>
+      <c r="W3" s="56"/>
+      <c r="X3" s="56"/>
+      <c r="Y3" s="56"/>
+      <c r="Z3" s="56"/>
+      <c r="AA3" s="56"/>
+      <c r="AB3" s="56"/>
+      <c r="AC3" s="56"/>
+      <c r="AD3" s="56"/>
+      <c r="AE3" s="56"/>
+      <c r="AF3" s="56"/>
+      <c r="AG3" s="56"/>
     </row>
     <row r="4" spans="1:33" ht="24">
       <c r="A4" s="4"/>
@@ -2216,25 +2152,25 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
-      <c r="H4" s="58" t="s">
+      <c r="H4" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="13" t="s">
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13" t="s">
+      <c r="L4" s="56"/>
+      <c r="M4" s="56"/>
+      <c r="N4" s="56"/>
+      <c r="O4" s="56"/>
+      <c r="P4" s="56"/>
+      <c r="Q4" s="56"/>
+      <c r="R4" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="S4" s="13"/>
-      <c r="T4" s="13"/>
+      <c r="S4" s="56"/>
+      <c r="T4" s="56"/>
       <c r="U4" s="4"/>
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
@@ -2245,11 +2181,11 @@
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
       <c r="AD4" s="4"/>
-      <c r="AE4" s="58" t="s">
+      <c r="AE4" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="AF4" s="58"/>
-      <c r="AG4" s="58"/>
+      <c r="AF4" s="57"/>
+      <c r="AG4" s="57"/>
     </row>
     <row r="5" spans="1:33" ht="6.75" customHeight="1" thickBot="1">
       <c r="A5" s="2"/>
@@ -2287,10 +2223,10 @@
       <c r="AG5" s="2"/>
     </row>
     <row r="6" spans="1:33" ht="16.5" customHeight="1" thickTop="1">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="61" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -2388,8 +2324,8 @@
       </c>
     </row>
     <row r="7" spans="1:33" ht="16.5" customHeight="1">
-      <c r="A7" s="53"/>
-      <c r="B7" s="55"/>
+      <c r="A7" s="60"/>
+      <c r="B7" s="62"/>
       <c r="C7" s="7">
         <v>1</v>
       </c>
@@ -2485,1727 +2421,1727 @@
       </c>
     </row>
     <row r="8" spans="1:33" ht="15" customHeight="1">
-      <c r="A8" s="56">
+      <c r="A8" s="63">
         <v>1</v>
       </c>
-      <c r="B8" s="78" t="s">
+      <c r="B8" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="51"/>
-      <c r="P8" s="51"/>
-      <c r="Q8" s="51"/>
-      <c r="R8" s="51"/>
-      <c r="S8" s="51"/>
-      <c r="T8" s="51"/>
-      <c r="U8" s="51"/>
-      <c r="V8" s="51"/>
-      <c r="W8" s="51"/>
-      <c r="X8" s="51"/>
-      <c r="Y8" s="51"/>
-      <c r="Z8" s="51"/>
-      <c r="AA8" s="30"/>
-      <c r="AB8" s="30"/>
-      <c r="AC8" s="30"/>
-      <c r="AD8" s="51"/>
-      <c r="AE8" s="51"/>
-      <c r="AF8" s="51"/>
-      <c r="AG8" s="51"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="44"/>
+      <c r="M8" s="44"/>
+      <c r="N8" s="44"/>
+      <c r="O8" s="44"/>
+      <c r="P8" s="44"/>
+      <c r="Q8" s="44"/>
+      <c r="R8" s="44"/>
+      <c r="S8" s="44"/>
+      <c r="T8" s="44"/>
+      <c r="U8" s="44"/>
+      <c r="V8" s="44"/>
+      <c r="W8" s="44"/>
+      <c r="X8" s="44"/>
+      <c r="Y8" s="44"/>
+      <c r="Z8" s="44"/>
+      <c r="AA8" s="44"/>
+      <c r="AB8" s="44"/>
+      <c r="AC8" s="44"/>
+      <c r="AD8" s="44"/>
+      <c r="AE8" s="44"/>
+      <c r="AF8" s="44"/>
+      <c r="AG8" s="44"/>
     </row>
     <row r="9" spans="1:33" ht="15" customHeight="1">
-      <c r="A9" s="47"/>
-      <c r="B9" s="79" t="s">
+      <c r="A9" s="53"/>
+      <c r="B9" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="45"/>
-      <c r="L9" s="45"/>
-      <c r="M9" s="45"/>
-      <c r="N9" s="45"/>
-      <c r="O9" s="45"/>
-      <c r="P9" s="45"/>
-      <c r="Q9" s="45"/>
-      <c r="R9" s="45"/>
-      <c r="S9" s="45"/>
-      <c r="T9" s="45"/>
-      <c r="U9" s="45"/>
-      <c r="V9" s="45"/>
-      <c r="W9" s="45"/>
-      <c r="X9" s="45"/>
-      <c r="Y9" s="45"/>
-      <c r="Z9" s="45"/>
-      <c r="AA9" s="28"/>
-      <c r="AB9" s="28"/>
-      <c r="AC9" s="28"/>
-      <c r="AD9" s="45"/>
-      <c r="AE9" s="45"/>
-      <c r="AF9" s="45"/>
-      <c r="AG9" s="45"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="40"/>
+      <c r="P9" s="40"/>
+      <c r="Q9" s="40"/>
+      <c r="R9" s="40"/>
+      <c r="S9" s="40"/>
+      <c r="T9" s="40"/>
+      <c r="U9" s="40"/>
+      <c r="V9" s="40"/>
+      <c r="W9" s="40"/>
+      <c r="X9" s="40"/>
+      <c r="Y9" s="40"/>
+      <c r="Z9" s="40"/>
+      <c r="AA9" s="40"/>
+      <c r="AB9" s="40"/>
+      <c r="AC9" s="40"/>
+      <c r="AD9" s="40"/>
+      <c r="AE9" s="40"/>
+      <c r="AF9" s="40"/>
+      <c r="AG9" s="40"/>
     </row>
     <row r="10" spans="1:33" ht="15" customHeight="1">
-      <c r="A10" s="46">
+      <c r="A10" s="52">
         <v>2</v>
       </c>
-      <c r="B10" s="80" t="s">
+      <c r="B10" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="49"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="49"/>
-      <c r="S10" s="33"/>
-      <c r="T10" s="33"/>
-      <c r="U10" s="33"/>
-      <c r="V10" s="49"/>
-      <c r="W10" s="49"/>
-      <c r="X10" s="49"/>
-      <c r="Y10" s="49"/>
-      <c r="Z10" s="49"/>
-      <c r="AA10" s="49"/>
-      <c r="AB10" s="49"/>
-      <c r="AC10" s="49"/>
-      <c r="AD10" s="49"/>
-      <c r="AE10" s="49"/>
-      <c r="AF10" s="49"/>
-      <c r="AG10" s="49"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36"/>
+      <c r="K10" s="64"/>
+      <c r="L10" s="36"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="65"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="65"/>
+      <c r="S10" s="36"/>
+      <c r="T10" s="36"/>
+      <c r="U10" s="36"/>
+      <c r="V10" s="65"/>
+      <c r="W10" s="65"/>
+      <c r="X10" s="65"/>
+      <c r="Y10" s="65"/>
+      <c r="Z10" s="65"/>
+      <c r="AA10" s="65"/>
+      <c r="AB10" s="65"/>
+      <c r="AC10" s="65"/>
+      <c r="AD10" s="65"/>
+      <c r="AE10" s="65"/>
+      <c r="AF10" s="65"/>
+      <c r="AG10" s="65"/>
     </row>
     <row r="11" spans="1:33" ht="15" customHeight="1">
-      <c r="A11" s="47"/>
-      <c r="B11" s="79" t="s">
+      <c r="A11" s="53"/>
+      <c r="B11" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="20"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="28"/>
-      <c r="O11" s="50"/>
-      <c r="P11" s="28"/>
-      <c r="Q11" s="28"/>
-      <c r="R11" s="50"/>
-      <c r="S11" s="28"/>
-      <c r="T11" s="28"/>
-      <c r="U11" s="28"/>
-      <c r="V11" s="50"/>
-      <c r="W11" s="50"/>
-      <c r="X11" s="50"/>
-      <c r="Y11" s="50"/>
-      <c r="Z11" s="50"/>
-      <c r="AA11" s="50"/>
-      <c r="AB11" s="50"/>
-      <c r="AC11" s="50"/>
-      <c r="AD11" s="50"/>
-      <c r="AE11" s="50"/>
-      <c r="AF11" s="50"/>
-      <c r="AG11" s="50"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="66"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="40"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="67"/>
+      <c r="P11" s="40"/>
+      <c r="Q11" s="40"/>
+      <c r="R11" s="67"/>
+      <c r="S11" s="40"/>
+      <c r="T11" s="40"/>
+      <c r="U11" s="40"/>
+      <c r="V11" s="67"/>
+      <c r="W11" s="67"/>
+      <c r="X11" s="67"/>
+      <c r="Y11" s="67"/>
+      <c r="Z11" s="67"/>
+      <c r="AA11" s="67"/>
+      <c r="AB11" s="67"/>
+      <c r="AC11" s="67"/>
+      <c r="AD11" s="67"/>
+      <c r="AE11" s="67"/>
+      <c r="AF11" s="67"/>
+      <c r="AG11" s="67"/>
     </row>
     <row r="12" spans="1:33" ht="15" customHeight="1">
-      <c r="A12" s="46">
+      <c r="A12" s="52">
         <v>3</v>
       </c>
-      <c r="B12" s="80" t="s">
+      <c r="B12" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="33"/>
-      <c r="M12" s="33"/>
-      <c r="N12" s="33"/>
-      <c r="O12" s="49"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="18"/>
-      <c r="R12" s="14"/>
-      <c r="S12" s="14"/>
-      <c r="T12" s="14"/>
-      <c r="U12" s="33"/>
-      <c r="V12" s="49"/>
-      <c r="W12" s="49"/>
-      <c r="X12" s="49"/>
-      <c r="Y12" s="49"/>
-      <c r="Z12" s="49"/>
-      <c r="AA12" s="49"/>
-      <c r="AB12" s="49"/>
-      <c r="AC12" s="49"/>
-      <c r="AD12" s="49"/>
-      <c r="AE12" s="49"/>
-      <c r="AF12" s="49"/>
-      <c r="AG12" s="49"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="65"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="64"/>
+      <c r="R12" s="36"/>
+      <c r="S12" s="36"/>
+      <c r="T12" s="36"/>
+      <c r="U12" s="36"/>
+      <c r="V12" s="65"/>
+      <c r="W12" s="65"/>
+      <c r="X12" s="65"/>
+      <c r="Y12" s="65"/>
+      <c r="Z12" s="65"/>
+      <c r="AA12" s="65"/>
+      <c r="AB12" s="65"/>
+      <c r="AC12" s="65"/>
+      <c r="AD12" s="65"/>
+      <c r="AE12" s="65"/>
+      <c r="AF12" s="65"/>
+      <c r="AG12" s="65"/>
     </row>
     <row r="13" spans="1:33" ht="15" customHeight="1">
-      <c r="A13" s="47"/>
-      <c r="B13" s="79" t="s">
+      <c r="A13" s="53"/>
+      <c r="B13" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
-      <c r="M13" s="28"/>
-      <c r="N13" s="28"/>
-      <c r="O13" s="50"/>
-      <c r="P13" s="28"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="20"/>
-      <c r="S13" s="20"/>
-      <c r="T13" s="20"/>
-      <c r="U13" s="28"/>
-      <c r="V13" s="50"/>
-      <c r="W13" s="50"/>
-      <c r="X13" s="50"/>
-      <c r="Y13" s="50"/>
-      <c r="Z13" s="50"/>
-      <c r="AA13" s="50"/>
-      <c r="AB13" s="50"/>
-      <c r="AC13" s="50"/>
-      <c r="AD13" s="50"/>
-      <c r="AE13" s="50"/>
-      <c r="AF13" s="50"/>
-      <c r="AG13" s="50"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="40"/>
+      <c r="N13" s="40"/>
+      <c r="O13" s="67"/>
+      <c r="P13" s="40"/>
+      <c r="Q13" s="66"/>
+      <c r="R13" s="40"/>
+      <c r="S13" s="40"/>
+      <c r="T13" s="40"/>
+      <c r="U13" s="40"/>
+      <c r="V13" s="67"/>
+      <c r="W13" s="67"/>
+      <c r="X13" s="67"/>
+      <c r="Y13" s="67"/>
+      <c r="Z13" s="67"/>
+      <c r="AA13" s="67"/>
+      <c r="AB13" s="67"/>
+      <c r="AC13" s="67"/>
+      <c r="AD13" s="67"/>
+      <c r="AE13" s="67"/>
+      <c r="AF13" s="67"/>
+      <c r="AG13" s="67"/>
     </row>
     <row r="14" spans="1:33" ht="15" customHeight="1">
-      <c r="A14" s="46">
+      <c r="A14" s="52">
         <v>4</v>
       </c>
-      <c r="B14" s="81"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="14"/>
-      <c r="T14" s="14"/>
-      <c r="U14" s="14"/>
-      <c r="V14" s="14"/>
-      <c r="W14" s="14"/>
-      <c r="X14" s="14"/>
-      <c r="Y14" s="14"/>
-      <c r="Z14" s="14"/>
-      <c r="AA14" s="14"/>
-      <c r="AB14" s="14"/>
-      <c r="AC14" s="14"/>
-      <c r="AD14" s="14"/>
-      <c r="AE14" s="14"/>
-      <c r="AF14" s="14"/>
-      <c r="AG14" s="14"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="64"/>
+      <c r="L14" s="36"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="65"/>
+      <c r="S14" s="36"/>
+      <c r="T14" s="36"/>
+      <c r="U14" s="36"/>
+      <c r="V14" s="36"/>
+      <c r="W14" s="36"/>
+      <c r="X14" s="36"/>
+      <c r="Y14" s="36"/>
+      <c r="Z14" s="36"/>
+      <c r="AA14" s="36"/>
+      <c r="AB14" s="36"/>
+      <c r="AC14" s="36"/>
+      <c r="AD14" s="36"/>
+      <c r="AE14" s="36"/>
+      <c r="AF14" s="36"/>
+      <c r="AG14" s="36"/>
     </row>
     <row r="15" spans="1:33" ht="15" customHeight="1">
-      <c r="A15" s="47"/>
-      <c r="B15" s="79"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="20"/>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="38"/>
-      <c r="S15" s="20"/>
-      <c r="T15" s="20"/>
-      <c r="U15" s="20"/>
-      <c r="V15" s="20"/>
-      <c r="W15" s="20"/>
-      <c r="X15" s="20"/>
-      <c r="Y15" s="20"/>
-      <c r="Z15" s="20"/>
-      <c r="AA15" s="20"/>
-      <c r="AB15" s="20"/>
-      <c r="AC15" s="20"/>
-      <c r="AD15" s="20"/>
-      <c r="AE15" s="20"/>
-      <c r="AF15" s="20"/>
-      <c r="AG15" s="20"/>
+      <c r="A15" s="53"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="66"/>
+      <c r="K15" s="66"/>
+      <c r="L15" s="40"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="40"/>
+      <c r="P15" s="40"/>
+      <c r="Q15" s="40"/>
+      <c r="R15" s="67"/>
+      <c r="S15" s="40"/>
+      <c r="T15" s="40"/>
+      <c r="U15" s="40"/>
+      <c r="V15" s="40"/>
+      <c r="W15" s="40"/>
+      <c r="X15" s="40"/>
+      <c r="Y15" s="40"/>
+      <c r="Z15" s="40"/>
+      <c r="AA15" s="40"/>
+      <c r="AB15" s="40"/>
+      <c r="AC15" s="40"/>
+      <c r="AD15" s="40"/>
+      <c r="AE15" s="40"/>
+      <c r="AF15" s="40"/>
+      <c r="AG15" s="40"/>
     </row>
     <row r="16" spans="1:33" ht="15" customHeight="1">
-      <c r="A16" s="46">
+      <c r="A16" s="52">
         <v>5</v>
       </c>
-      <c r="B16" s="81"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="14"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="14"/>
-      <c r="T16" s="14"/>
-      <c r="U16" s="14"/>
-      <c r="V16" s="14"/>
-      <c r="W16" s="14"/>
-      <c r="X16" s="18"/>
-      <c r="Y16" s="14"/>
-      <c r="Z16" s="14"/>
-      <c r="AA16" s="18"/>
-      <c r="AB16" s="14"/>
-      <c r="AC16" s="14"/>
-      <c r="AD16" s="44"/>
-      <c r="AE16" s="14"/>
-      <c r="AF16" s="39"/>
-      <c r="AG16" s="14"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="65"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="64"/>
+      <c r="K16" s="64"/>
+      <c r="L16" s="36"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="65"/>
+      <c r="S16" s="36"/>
+      <c r="T16" s="36"/>
+      <c r="U16" s="36"/>
+      <c r="V16" s="36"/>
+      <c r="W16" s="36"/>
+      <c r="X16" s="64"/>
+      <c r="Y16" s="36"/>
+      <c r="Z16" s="36"/>
+      <c r="AA16" s="64"/>
+      <c r="AB16" s="36"/>
+      <c r="AC16" s="36"/>
+      <c r="AD16" s="43"/>
+      <c r="AE16" s="36"/>
+      <c r="AF16" s="50"/>
+      <c r="AG16" s="36"/>
     </row>
     <row r="17" spans="1:40" ht="15" customHeight="1">
-      <c r="A17" s="47"/>
-      <c r="B17" s="79"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="20"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="20"/>
-      <c r="P17" s="20"/>
-      <c r="Q17" s="20"/>
-      <c r="R17" s="38"/>
-      <c r="S17" s="20"/>
-      <c r="T17" s="20"/>
-      <c r="U17" s="20"/>
-      <c r="V17" s="20"/>
-      <c r="W17" s="20"/>
-      <c r="X17" s="23"/>
-      <c r="Y17" s="20"/>
-      <c r="Z17" s="20"/>
-      <c r="AA17" s="23"/>
-      <c r="AB17" s="20"/>
-      <c r="AC17" s="20"/>
-      <c r="AD17" s="45"/>
-      <c r="AE17" s="20"/>
-      <c r="AF17" s="48"/>
-      <c r="AG17" s="20"/>
+      <c r="A17" s="53"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="66"/>
+      <c r="K17" s="66"/>
+      <c r="L17" s="40"/>
+      <c r="M17" s="40"/>
+      <c r="N17" s="40"/>
+      <c r="O17" s="40"/>
+      <c r="P17" s="40"/>
+      <c r="Q17" s="40"/>
+      <c r="R17" s="67"/>
+      <c r="S17" s="40"/>
+      <c r="T17" s="40"/>
+      <c r="U17" s="40"/>
+      <c r="V17" s="40"/>
+      <c r="W17" s="40"/>
+      <c r="X17" s="66"/>
+      <c r="Y17" s="40"/>
+      <c r="Z17" s="40"/>
+      <c r="AA17" s="66"/>
+      <c r="AB17" s="40"/>
+      <c r="AC17" s="40"/>
+      <c r="AD17" s="40"/>
+      <c r="AE17" s="40"/>
+      <c r="AF17" s="54"/>
+      <c r="AG17" s="40"/>
     </row>
     <row r="18" spans="1:40" ht="15" customHeight="1">
-      <c r="A18" s="46">
+      <c r="A18" s="52">
         <v>6</v>
       </c>
-      <c r="B18" s="81"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="16"/>
-      <c r="S18" s="14"/>
-      <c r="T18" s="14"/>
-      <c r="U18" s="14"/>
-      <c r="V18" s="14"/>
-      <c r="W18" s="14"/>
-      <c r="X18" s="18"/>
-      <c r="Y18" s="14"/>
-      <c r="Z18" s="14"/>
-      <c r="AA18" s="14"/>
-      <c r="AB18" s="14"/>
-      <c r="AC18" s="14"/>
-      <c r="AD18" s="44"/>
-      <c r="AE18" s="44"/>
-      <c r="AF18" s="44"/>
-      <c r="AG18" s="44"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="64"/>
+      <c r="K18" s="64"/>
+      <c r="L18" s="36"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="65"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="65"/>
+      <c r="S18" s="36"/>
+      <c r="T18" s="36"/>
+      <c r="U18" s="36"/>
+      <c r="V18" s="36"/>
+      <c r="W18" s="36"/>
+      <c r="X18" s="64"/>
+      <c r="Y18" s="36"/>
+      <c r="Z18" s="36"/>
+      <c r="AA18" s="36"/>
+      <c r="AB18" s="36"/>
+      <c r="AC18" s="36"/>
+      <c r="AD18" s="43"/>
+      <c r="AE18" s="43"/>
+      <c r="AF18" s="43"/>
+      <c r="AG18" s="43"/>
     </row>
     <row r="19" spans="1:40" ht="15" customHeight="1">
-      <c r="A19" s="47"/>
-      <c r="B19" s="79"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="23"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="20"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="38"/>
-      <c r="P19" s="20"/>
-      <c r="Q19" s="20"/>
-      <c r="R19" s="38"/>
-      <c r="S19" s="20"/>
-      <c r="T19" s="20"/>
-      <c r="U19" s="20"/>
-      <c r="V19" s="20"/>
-      <c r="W19" s="20"/>
-      <c r="X19" s="23"/>
-      <c r="Y19" s="20"/>
-      <c r="Z19" s="20"/>
-      <c r="AA19" s="20"/>
-      <c r="AB19" s="20"/>
-      <c r="AC19" s="20"/>
-      <c r="AD19" s="45"/>
-      <c r="AE19" s="45"/>
-      <c r="AF19" s="45"/>
-      <c r="AG19" s="45"/>
+      <c r="A19" s="53"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="66"/>
+      <c r="K19" s="66"/>
+      <c r="L19" s="40"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="40"/>
+      <c r="O19" s="67"/>
+      <c r="P19" s="40"/>
+      <c r="Q19" s="40"/>
+      <c r="R19" s="67"/>
+      <c r="S19" s="40"/>
+      <c r="T19" s="40"/>
+      <c r="U19" s="40"/>
+      <c r="V19" s="40"/>
+      <c r="W19" s="40"/>
+      <c r="X19" s="66"/>
+      <c r="Y19" s="40"/>
+      <c r="Z19" s="40"/>
+      <c r="AA19" s="40"/>
+      <c r="AB19" s="40"/>
+      <c r="AC19" s="40"/>
+      <c r="AD19" s="40"/>
+      <c r="AE19" s="40"/>
+      <c r="AF19" s="40"/>
+      <c r="AG19" s="40"/>
     </row>
     <row r="20" spans="1:40" ht="15" customHeight="1">
-      <c r="A20" s="46">
+      <c r="A20" s="52">
         <v>7</v>
       </c>
-      <c r="B20" s="81"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="16"/>
-      <c r="S20" s="14"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="14"/>
-      <c r="V20" s="14"/>
-      <c r="W20" s="14"/>
-      <c r="X20" s="14"/>
-      <c r="Y20" s="14"/>
-      <c r="Z20" s="14"/>
-      <c r="AA20" s="14"/>
-      <c r="AB20" s="26"/>
-      <c r="AC20" s="14"/>
-      <c r="AD20" s="44"/>
-      <c r="AE20" s="44"/>
-      <c r="AF20" s="44"/>
-      <c r="AG20" s="44"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="65"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="64"/>
+      <c r="K20" s="64"/>
+      <c r="L20" s="36"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="65"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="65"/>
+      <c r="S20" s="36"/>
+      <c r="T20" s="36"/>
+      <c r="U20" s="36"/>
+      <c r="V20" s="36"/>
+      <c r="W20" s="36"/>
+      <c r="X20" s="36"/>
+      <c r="Y20" s="36"/>
+      <c r="Z20" s="36"/>
+      <c r="AA20" s="36"/>
+      <c r="AB20" s="43"/>
+      <c r="AC20" s="36"/>
+      <c r="AD20" s="43"/>
+      <c r="AE20" s="43"/>
+      <c r="AF20" s="43"/>
+      <c r="AG20" s="43"/>
     </row>
     <row r="21" spans="1:40" ht="15" customHeight="1">
-      <c r="A21" s="47"/>
-      <c r="B21" s="79"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="20"/>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="38"/>
-      <c r="P21" s="20"/>
-      <c r="Q21" s="20"/>
-      <c r="R21" s="38"/>
-      <c r="S21" s="20"/>
-      <c r="T21" s="20"/>
-      <c r="U21" s="20"/>
-      <c r="V21" s="20"/>
-      <c r="W21" s="20"/>
-      <c r="X21" s="20"/>
-      <c r="Y21" s="20"/>
-      <c r="Z21" s="20"/>
-      <c r="AA21" s="20"/>
-      <c r="AB21" s="20"/>
-      <c r="AC21" s="20"/>
-      <c r="AD21" s="45"/>
-      <c r="AE21" s="45"/>
-      <c r="AF21" s="45"/>
-      <c r="AG21" s="45"/>
+      <c r="A21" s="53"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="66"/>
+      <c r="K21" s="66"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="40"/>
+      <c r="O21" s="67"/>
+      <c r="P21" s="40"/>
+      <c r="Q21" s="40"/>
+      <c r="R21" s="67"/>
+      <c r="S21" s="40"/>
+      <c r="T21" s="40"/>
+      <c r="U21" s="40"/>
+      <c r="V21" s="40"/>
+      <c r="W21" s="40"/>
+      <c r="X21" s="40"/>
+      <c r="Y21" s="40"/>
+      <c r="Z21" s="40"/>
+      <c r="AA21" s="40"/>
+      <c r="AB21" s="40"/>
+      <c r="AC21" s="40"/>
+      <c r="AD21" s="40"/>
+      <c r="AE21" s="40"/>
+      <c r="AF21" s="40"/>
+      <c r="AG21" s="40"/>
     </row>
     <row r="22" spans="1:40" ht="15" customHeight="1">
-      <c r="A22" s="21">
+      <c r="A22" s="38">
         <v>8</v>
       </c>
-      <c r="B22" s="81"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="14"/>
-      <c r="Q22" s="18"/>
-      <c r="R22" s="14"/>
-      <c r="S22" s="14"/>
-      <c r="T22" s="14"/>
-      <c r="U22" s="14"/>
-      <c r="V22" s="14"/>
-      <c r="W22" s="14"/>
-      <c r="X22" s="16"/>
-      <c r="Y22" s="16"/>
-      <c r="Z22" s="42"/>
-      <c r="AA22" s="26"/>
-      <c r="AB22" s="26"/>
-      <c r="AC22" s="26"/>
-      <c r="AD22" s="14"/>
-      <c r="AE22" s="39"/>
-      <c r="AF22" s="39"/>
-      <c r="AG22" s="14"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="64"/>
+      <c r="R22" s="36"/>
+      <c r="S22" s="36"/>
+      <c r="T22" s="36"/>
+      <c r="U22" s="36"/>
+      <c r="V22" s="36"/>
+      <c r="W22" s="36"/>
+      <c r="X22" s="65"/>
+      <c r="Y22" s="65"/>
+      <c r="Z22" s="43"/>
+      <c r="AA22" s="43"/>
+      <c r="AB22" s="43"/>
+      <c r="AC22" s="43"/>
+      <c r="AD22" s="36"/>
+      <c r="AE22" s="50"/>
+      <c r="AF22" s="50"/>
+      <c r="AG22" s="36"/>
     </row>
     <row r="23" spans="1:40" ht="15" customHeight="1">
-      <c r="A23" s="24"/>
-      <c r="B23" s="79"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="26"/>
-      <c r="P23" s="26"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="15"/>
-      <c r="S23" s="15"/>
-      <c r="T23" s="15"/>
-      <c r="U23" s="15"/>
-      <c r="V23" s="15"/>
-      <c r="W23" s="15"/>
-      <c r="X23" s="34"/>
-      <c r="Y23" s="17"/>
-      <c r="Z23" s="43"/>
-      <c r="AA23" s="26"/>
-      <c r="AB23" s="26"/>
-      <c r="AC23" s="26"/>
-      <c r="AD23" s="26"/>
-      <c r="AE23" s="40"/>
-      <c r="AF23" s="40"/>
-      <c r="AG23" s="26"/>
+      <c r="A23" s="41"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="40"/>
+      <c r="L23" s="43"/>
+      <c r="M23" s="43"/>
+      <c r="N23" s="43"/>
+      <c r="O23" s="43"/>
+      <c r="P23" s="43"/>
+      <c r="Q23" s="69"/>
+      <c r="R23" s="37"/>
+      <c r="S23" s="37"/>
+      <c r="T23" s="37"/>
+      <c r="U23" s="37"/>
+      <c r="V23" s="37"/>
+      <c r="W23" s="37"/>
+      <c r="X23" s="68"/>
+      <c r="Y23" s="70"/>
+      <c r="Z23" s="37"/>
+      <c r="AA23" s="43"/>
+      <c r="AB23" s="43"/>
+      <c r="AC23" s="43"/>
+      <c r="AD23" s="43"/>
+      <c r="AE23" s="51"/>
+      <c r="AF23" s="51"/>
+      <c r="AG23" s="43"/>
     </row>
     <row r="24" spans="1:40" ht="15" customHeight="1">
-      <c r="A24" s="41">
+      <c r="A24" s="49">
         <v>9</v>
       </c>
-      <c r="B24" s="78" t="s">
+      <c r="B24" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="29"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
-      <c r="O24" s="30"/>
-      <c r="P24" s="29"/>
-      <c r="Q24" s="29"/>
-      <c r="R24" s="29"/>
-      <c r="S24" s="29"/>
-      <c r="T24" s="29"/>
-      <c r="U24" s="29"/>
-      <c r="V24" s="29"/>
-      <c r="W24" s="29"/>
-      <c r="X24" s="29"/>
-      <c r="Y24" s="29"/>
-      <c r="Z24" s="29"/>
-      <c r="AA24" s="30"/>
-      <c r="AB24" s="30"/>
-      <c r="AC24" s="29"/>
-      <c r="AD24" s="29"/>
-      <c r="AE24" s="29"/>
-      <c r="AF24" s="29"/>
-      <c r="AG24" s="29"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="44"/>
+      <c r="K24" s="44"/>
+      <c r="L24" s="44"/>
+      <c r="M24" s="44"/>
+      <c r="N24" s="44"/>
+      <c r="O24" s="44"/>
+      <c r="P24" s="44"/>
+      <c r="Q24" s="44"/>
+      <c r="R24" s="44"/>
+      <c r="S24" s="44"/>
+      <c r="T24" s="44"/>
+      <c r="U24" s="44"/>
+      <c r="V24" s="44"/>
+      <c r="W24" s="44"/>
+      <c r="X24" s="44"/>
+      <c r="Y24" s="44"/>
+      <c r="Z24" s="44"/>
+      <c r="AA24" s="44"/>
+      <c r="AB24" s="44"/>
+      <c r="AC24" s="44"/>
+      <c r="AD24" s="44"/>
+      <c r="AE24" s="44"/>
+      <c r="AF24" s="44"/>
+      <c r="AG24" s="44"/>
     </row>
     <row r="25" spans="1:40" ht="15" customHeight="1">
-      <c r="A25" s="37"/>
-      <c r="B25" s="79" t="s">
+      <c r="A25" s="48"/>
+      <c r="B25" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="28"/>
-      <c r="N25" s="28"/>
-      <c r="O25" s="28"/>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
-      <c r="R25" s="20"/>
-      <c r="S25" s="20"/>
-      <c r="T25" s="20"/>
-      <c r="U25" s="20"/>
-      <c r="V25" s="20"/>
-      <c r="W25" s="20"/>
-      <c r="X25" s="20"/>
-      <c r="Y25" s="20"/>
-      <c r="Z25" s="20"/>
-      <c r="AA25" s="28"/>
-      <c r="AB25" s="28"/>
-      <c r="AC25" s="20"/>
-      <c r="AD25" s="20"/>
-      <c r="AE25" s="20"/>
-      <c r="AF25" s="20"/>
-      <c r="AG25" s="20"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="66"/>
+      <c r="J25" s="40"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="40"/>
+      <c r="M25" s="40"/>
+      <c r="N25" s="40"/>
+      <c r="O25" s="40"/>
+      <c r="P25" s="40"/>
+      <c r="Q25" s="40"/>
+      <c r="R25" s="40"/>
+      <c r="S25" s="40"/>
+      <c r="T25" s="40"/>
+      <c r="U25" s="40"/>
+      <c r="V25" s="40"/>
+      <c r="W25" s="40"/>
+      <c r="X25" s="40"/>
+      <c r="Y25" s="40"/>
+      <c r="Z25" s="40"/>
+      <c r="AA25" s="40"/>
+      <c r="AB25" s="40"/>
+      <c r="AC25" s="40"/>
+      <c r="AD25" s="40"/>
+      <c r="AE25" s="40"/>
+      <c r="AF25" s="40"/>
+      <c r="AG25" s="40"/>
     </row>
     <row r="26" spans="1:40" ht="15" customHeight="1">
-      <c r="A26" s="35">
+      <c r="A26" s="46">
         <v>10</v>
       </c>
-      <c r="B26" s="81"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="18"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="14"/>
-      <c r="P26" s="14"/>
-      <c r="Q26" s="14"/>
-      <c r="R26" s="14"/>
-      <c r="S26" s="14"/>
-      <c r="T26" s="14"/>
-      <c r="U26" s="14"/>
-      <c r="V26" s="14"/>
-      <c r="W26" s="14"/>
-      <c r="X26" s="14"/>
-      <c r="Y26" s="14"/>
-      <c r="Z26" s="14"/>
-      <c r="AA26" s="18"/>
-      <c r="AB26" s="14"/>
-      <c r="AC26" s="14"/>
-      <c r="AD26" s="14"/>
-      <c r="AE26" s="14"/>
-      <c r="AF26" s="14"/>
-      <c r="AG26" s="14"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="36"/>
+      <c r="J26" s="36"/>
+      <c r="K26" s="36"/>
+      <c r="L26" s="64"/>
+      <c r="M26" s="36"/>
+      <c r="N26" s="36"/>
+      <c r="O26" s="36"/>
+      <c r="P26" s="36"/>
+      <c r="Q26" s="36"/>
+      <c r="R26" s="36"/>
+      <c r="S26" s="36"/>
+      <c r="T26" s="36"/>
+      <c r="U26" s="36"/>
+      <c r="V26" s="36"/>
+      <c r="W26" s="36"/>
+      <c r="X26" s="36"/>
+      <c r="Y26" s="36"/>
+      <c r="Z26" s="36"/>
+      <c r="AA26" s="64"/>
+      <c r="AB26" s="36"/>
+      <c r="AC26" s="36"/>
+      <c r="AD26" s="36"/>
+      <c r="AE26" s="36"/>
+      <c r="AF26" s="36"/>
+      <c r="AG26" s="36"/>
     </row>
     <row r="27" spans="1:40" ht="15" customHeight="1">
-      <c r="A27" s="37"/>
-      <c r="B27" s="79"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="23"/>
-      <c r="M27" s="20"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="20"/>
-      <c r="P27" s="20"/>
-      <c r="Q27" s="20"/>
-      <c r="R27" s="20"/>
-      <c r="S27" s="20"/>
-      <c r="T27" s="20"/>
-      <c r="U27" s="20"/>
-      <c r="V27" s="20"/>
-      <c r="W27" s="20"/>
-      <c r="X27" s="20"/>
-      <c r="Y27" s="20"/>
-      <c r="Z27" s="20"/>
-      <c r="AA27" s="23"/>
-      <c r="AB27" s="20"/>
-      <c r="AC27" s="20"/>
-      <c r="AD27" s="20"/>
-      <c r="AE27" s="20"/>
-      <c r="AF27" s="20"/>
-      <c r="AG27" s="20"/>
+      <c r="A27" s="48"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="40"/>
+      <c r="K27" s="40"/>
+      <c r="L27" s="66"/>
+      <c r="M27" s="40"/>
+      <c r="N27" s="40"/>
+      <c r="O27" s="40"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="40"/>
+      <c r="S27" s="40"/>
+      <c r="T27" s="40"/>
+      <c r="U27" s="40"/>
+      <c r="V27" s="40"/>
+      <c r="W27" s="40"/>
+      <c r="X27" s="40"/>
+      <c r="Y27" s="40"/>
+      <c r="Z27" s="40"/>
+      <c r="AA27" s="66"/>
+      <c r="AB27" s="40"/>
+      <c r="AC27" s="40"/>
+      <c r="AD27" s="40"/>
+      <c r="AE27" s="40"/>
+      <c r="AF27" s="40"/>
+      <c r="AG27" s="40"/>
     </row>
     <row r="28" spans="1:40" ht="15" customHeight="1">
-      <c r="A28" s="35">
+      <c r="A28" s="46">
         <v>11</v>
       </c>
-      <c r="B28" s="81"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
-      <c r="O28" s="14"/>
-      <c r="P28" s="14"/>
-      <c r="Q28" s="14"/>
-      <c r="R28" s="14"/>
-      <c r="S28" s="14"/>
-      <c r="T28" s="14"/>
-      <c r="U28" s="14"/>
-      <c r="V28" s="14"/>
-      <c r="W28" s="14"/>
-      <c r="X28" s="14"/>
-      <c r="Y28" s="14"/>
-      <c r="Z28" s="14"/>
-      <c r="AA28" s="14"/>
-      <c r="AB28" s="14"/>
-      <c r="AC28" s="14"/>
-      <c r="AD28" s="26"/>
-      <c r="AE28" s="26"/>
-      <c r="AF28" s="26"/>
-      <c r="AG28" s="26"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="65"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="65"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="64"/>
+      <c r="J28" s="36"/>
+      <c r="K28" s="36"/>
+      <c r="L28" s="36"/>
+      <c r="M28" s="36"/>
+      <c r="N28" s="36"/>
+      <c r="O28" s="36"/>
+      <c r="P28" s="36"/>
+      <c r="Q28" s="36"/>
+      <c r="R28" s="36"/>
+      <c r="S28" s="36"/>
+      <c r="T28" s="36"/>
+      <c r="U28" s="36"/>
+      <c r="V28" s="36"/>
+      <c r="W28" s="36"/>
+      <c r="X28" s="36"/>
+      <c r="Y28" s="36"/>
+      <c r="Z28" s="36"/>
+      <c r="AA28" s="36"/>
+      <c r="AB28" s="36"/>
+      <c r="AC28" s="36"/>
+      <c r="AD28" s="43"/>
+      <c r="AE28" s="43"/>
+      <c r="AF28" s="43"/>
+      <c r="AG28" s="43"/>
     </row>
     <row r="29" spans="1:40" ht="15" customHeight="1">
-      <c r="A29" s="37"/>
-      <c r="B29" s="79"/>
-      <c r="C29" s="38"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="20"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="20"/>
-      <c r="P29" s="20"/>
-      <c r="Q29" s="20"/>
-      <c r="R29" s="20"/>
-      <c r="S29" s="20"/>
-      <c r="T29" s="20"/>
-      <c r="U29" s="20"/>
-      <c r="V29" s="20"/>
-      <c r="W29" s="20"/>
-      <c r="X29" s="20"/>
-      <c r="Y29" s="20"/>
-      <c r="Z29" s="20"/>
-      <c r="AA29" s="20"/>
-      <c r="AB29" s="20"/>
-      <c r="AC29" s="20"/>
-      <c r="AD29" s="20"/>
-      <c r="AE29" s="20"/>
-      <c r="AF29" s="20"/>
-      <c r="AG29" s="20"/>
+      <c r="A29" s="48"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="67"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="66"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="40"/>
+      <c r="M29" s="40"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="40"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="40"/>
+      <c r="S29" s="40"/>
+      <c r="T29" s="40"/>
+      <c r="U29" s="40"/>
+      <c r="V29" s="40"/>
+      <c r="W29" s="40"/>
+      <c r="X29" s="40"/>
+      <c r="Y29" s="40"/>
+      <c r="Z29" s="40"/>
+      <c r="AA29" s="40"/>
+      <c r="AB29" s="40"/>
+      <c r="AC29" s="40"/>
+      <c r="AD29" s="40"/>
+      <c r="AE29" s="40"/>
+      <c r="AF29" s="40"/>
+      <c r="AG29" s="40"/>
     </row>
     <row r="30" spans="1:40" ht="15" customHeight="1">
-      <c r="A30" s="35">
+      <c r="A30" s="46">
         <v>12</v>
       </c>
-      <c r="B30" s="81"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="18"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="14"/>
-      <c r="P30" s="14"/>
-      <c r="Q30" s="14"/>
-      <c r="R30" s="14"/>
-      <c r="S30" s="14"/>
-      <c r="T30" s="14"/>
-      <c r="U30" s="14"/>
-      <c r="V30" s="14"/>
-      <c r="W30" s="33"/>
-      <c r="X30" s="16"/>
-      <c r="Y30" s="14"/>
-      <c r="Z30" s="33"/>
-      <c r="AA30" s="18"/>
-      <c r="AB30" s="14"/>
-      <c r="AC30" s="14"/>
-      <c r="AD30" s="14"/>
-      <c r="AE30" s="14"/>
-      <c r="AF30" s="14"/>
-      <c r="AG30" s="14"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="64"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="64"/>
+      <c r="M30" s="36"/>
+      <c r="N30" s="36"/>
+      <c r="O30" s="36"/>
+      <c r="P30" s="36"/>
+      <c r="Q30" s="36"/>
+      <c r="R30" s="36"/>
+      <c r="S30" s="36"/>
+      <c r="T30" s="36"/>
+      <c r="U30" s="36"/>
+      <c r="V30" s="36"/>
+      <c r="W30" s="36"/>
+      <c r="X30" s="65"/>
+      <c r="Y30" s="36"/>
+      <c r="Z30" s="36"/>
+      <c r="AA30" s="64"/>
+      <c r="AB30" s="36"/>
+      <c r="AC30" s="36"/>
+      <c r="AD30" s="36"/>
+      <c r="AE30" s="36"/>
+      <c r="AF30" s="36"/>
+      <c r="AG30" s="36"/>
       <c r="AN30" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:40" ht="15" customHeight="1">
-      <c r="A31" s="36"/>
-      <c r="B31" s="80"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="26"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="15"/>
-      <c r="O31" s="15"/>
-      <c r="P31" s="26"/>
-      <c r="Q31" s="26"/>
-      <c r="R31" s="26"/>
-      <c r="S31" s="26"/>
-      <c r="T31" s="26"/>
-      <c r="U31" s="26"/>
-      <c r="V31" s="26"/>
-      <c r="W31" s="27"/>
-      <c r="X31" s="34"/>
-      <c r="Y31" s="26"/>
-      <c r="Z31" s="27"/>
-      <c r="AA31" s="19"/>
-      <c r="AB31" s="15"/>
-      <c r="AC31" s="26"/>
-      <c r="AD31" s="26"/>
-      <c r="AE31" s="26"/>
-      <c r="AF31" s="26"/>
-      <c r="AG31" s="26"/>
+      <c r="A31" s="47"/>
+      <c r="B31" s="23"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="69"/>
+      <c r="J31" s="37"/>
+      <c r="K31" s="43"/>
+      <c r="L31" s="69"/>
+      <c r="M31" s="37"/>
+      <c r="N31" s="37"/>
+      <c r="O31" s="37"/>
+      <c r="P31" s="43"/>
+      <c r="Q31" s="43"/>
+      <c r="R31" s="43"/>
+      <c r="S31" s="43"/>
+      <c r="T31" s="43"/>
+      <c r="U31" s="43"/>
+      <c r="V31" s="43"/>
+      <c r="W31" s="43"/>
+      <c r="X31" s="68"/>
+      <c r="Y31" s="43"/>
+      <c r="Z31" s="43"/>
+      <c r="AA31" s="69"/>
+      <c r="AB31" s="37"/>
+      <c r="AC31" s="43"/>
+      <c r="AD31" s="43"/>
+      <c r="AE31" s="43"/>
+      <c r="AF31" s="43"/>
+      <c r="AG31" s="43"/>
     </row>
     <row r="32" spans="1:40" ht="15" customHeight="1">
-      <c r="A32" s="31">
+      <c r="A32" s="45">
         <v>13</v>
       </c>
-      <c r="B32" s="78" t="s">
+      <c r="B32" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="29"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="30"/>
-      <c r="S32" s="30"/>
-      <c r="T32" s="30"/>
-      <c r="U32" s="30"/>
-      <c r="V32" s="29"/>
-      <c r="W32" s="29"/>
-      <c r="X32" s="29"/>
-      <c r="Y32" s="29"/>
-      <c r="Z32" s="29"/>
-      <c r="AA32" s="29"/>
-      <c r="AB32" s="29"/>
-      <c r="AC32" s="29"/>
-      <c r="AD32" s="29"/>
-      <c r="AE32" s="29"/>
-      <c r="AF32" s="29"/>
-      <c r="AG32" s="29"/>
+      <c r="C32" s="44"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="44"/>
+      <c r="J32" s="44"/>
+      <c r="K32" s="44"/>
+      <c r="L32" s="44"/>
+      <c r="M32" s="44"/>
+      <c r="N32" s="44"/>
+      <c r="O32" s="44"/>
+      <c r="P32" s="44"/>
+      <c r="Q32" s="44"/>
+      <c r="R32" s="44"/>
+      <c r="S32" s="44"/>
+      <c r="T32" s="44"/>
+      <c r="U32" s="44"/>
+      <c r="V32" s="44"/>
+      <c r="W32" s="44"/>
+      <c r="X32" s="44"/>
+      <c r="Y32" s="44"/>
+      <c r="Z32" s="44"/>
+      <c r="AA32" s="44"/>
+      <c r="AB32" s="44"/>
+      <c r="AC32" s="44"/>
+      <c r="AD32" s="44"/>
+      <c r="AE32" s="44"/>
+      <c r="AF32" s="44"/>
+      <c r="AG32" s="44"/>
     </row>
     <row r="33" spans="1:33" ht="15" customHeight="1">
-      <c r="A33" s="25"/>
-      <c r="B33" s="79" t="s">
+      <c r="A33" s="42"/>
+      <c r="B33" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="20"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="20"/>
-      <c r="L33" s="20"/>
-      <c r="M33" s="20"/>
-      <c r="N33" s="20"/>
-      <c r="O33" s="20"/>
-      <c r="P33" s="20"/>
-      <c r="Q33" s="20"/>
-      <c r="R33" s="28"/>
-      <c r="S33" s="28"/>
-      <c r="T33" s="28"/>
-      <c r="U33" s="28"/>
-      <c r="V33" s="20"/>
-      <c r="W33" s="20"/>
-      <c r="X33" s="20"/>
-      <c r="Y33" s="20"/>
-      <c r="Z33" s="20"/>
-      <c r="AA33" s="20"/>
-      <c r="AB33" s="20"/>
-      <c r="AC33" s="20"/>
-      <c r="AD33" s="20"/>
-      <c r="AE33" s="20"/>
-      <c r="AF33" s="20"/>
-      <c r="AG33" s="20"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="66"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="40"/>
+      <c r="J33" s="40"/>
+      <c r="K33" s="40"/>
+      <c r="L33" s="40"/>
+      <c r="M33" s="40"/>
+      <c r="N33" s="40"/>
+      <c r="O33" s="40"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="40"/>
+      <c r="R33" s="40"/>
+      <c r="S33" s="40"/>
+      <c r="T33" s="40"/>
+      <c r="U33" s="40"/>
+      <c r="V33" s="40"/>
+      <c r="W33" s="40"/>
+      <c r="X33" s="40"/>
+      <c r="Y33" s="40"/>
+      <c r="Z33" s="40"/>
+      <c r="AA33" s="40"/>
+      <c r="AB33" s="40"/>
+      <c r="AC33" s="40"/>
+      <c r="AD33" s="40"/>
+      <c r="AE33" s="40"/>
+      <c r="AF33" s="40"/>
+      <c r="AG33" s="40"/>
     </row>
     <row r="34" spans="1:33" ht="15" customHeight="1">
-      <c r="A34" s="24">
+      <c r="A34" s="41">
         <v>14</v>
       </c>
-      <c r="B34" s="80" t="s">
+      <c r="B34" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="26"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="14"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="14"/>
-      <c r="O34" s="14"/>
-      <c r="P34" s="14"/>
-      <c r="Q34" s="14"/>
-      <c r="R34" s="18"/>
-      <c r="S34" s="14"/>
-      <c r="T34" s="14"/>
-      <c r="U34" s="14"/>
-      <c r="V34" s="14"/>
-      <c r="W34" s="14"/>
-      <c r="X34" s="14"/>
-      <c r="Y34" s="14"/>
-      <c r="Z34" s="14"/>
-      <c r="AA34" s="14"/>
-      <c r="AB34" s="14"/>
-      <c r="AC34" s="14"/>
-      <c r="AD34" s="14"/>
-      <c r="AE34" s="14"/>
-      <c r="AF34" s="14"/>
-      <c r="AG34" s="14"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="36"/>
+      <c r="J34" s="36"/>
+      <c r="K34" s="36"/>
+      <c r="L34" s="36"/>
+      <c r="M34" s="36"/>
+      <c r="N34" s="36"/>
+      <c r="O34" s="36"/>
+      <c r="P34" s="36"/>
+      <c r="Q34" s="36"/>
+      <c r="R34" s="64"/>
+      <c r="S34" s="36"/>
+      <c r="T34" s="36"/>
+      <c r="U34" s="36"/>
+      <c r="V34" s="36"/>
+      <c r="W34" s="36"/>
+      <c r="X34" s="36"/>
+      <c r="Y34" s="36"/>
+      <c r="Z34" s="36"/>
+      <c r="AA34" s="36"/>
+      <c r="AB34" s="36"/>
+      <c r="AC34" s="36"/>
+      <c r="AD34" s="36"/>
+      <c r="AE34" s="36"/>
+      <c r="AF34" s="36"/>
+      <c r="AG34" s="36"/>
     </row>
     <row r="35" spans="1:33" ht="15" customHeight="1">
-      <c r="A35" s="25"/>
-      <c r="B35" s="79" t="s">
+      <c r="A35" s="42"/>
+      <c r="B35" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C35" s="20"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="20"/>
-      <c r="L35" s="20"/>
-      <c r="M35" s="20"/>
-      <c r="N35" s="20"/>
-      <c r="O35" s="20"/>
-      <c r="P35" s="20"/>
-      <c r="Q35" s="20"/>
-      <c r="R35" s="23"/>
-      <c r="S35" s="20"/>
-      <c r="T35" s="20"/>
-      <c r="U35" s="20"/>
-      <c r="V35" s="20"/>
-      <c r="W35" s="20"/>
-      <c r="X35" s="20"/>
-      <c r="Y35" s="20"/>
-      <c r="Z35" s="20"/>
-      <c r="AA35" s="20"/>
-      <c r="AB35" s="20"/>
-      <c r="AC35" s="20"/>
-      <c r="AD35" s="20"/>
-      <c r="AE35" s="20"/>
-      <c r="AF35" s="20"/>
-      <c r="AG35" s="20"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="40"/>
+      <c r="J35" s="40"/>
+      <c r="K35" s="40"/>
+      <c r="L35" s="40"/>
+      <c r="M35" s="40"/>
+      <c r="N35" s="40"/>
+      <c r="O35" s="40"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="66"/>
+      <c r="S35" s="40"/>
+      <c r="T35" s="40"/>
+      <c r="U35" s="40"/>
+      <c r="V35" s="40"/>
+      <c r="W35" s="40"/>
+      <c r="X35" s="40"/>
+      <c r="Y35" s="40"/>
+      <c r="Z35" s="40"/>
+      <c r="AA35" s="40"/>
+      <c r="AB35" s="40"/>
+      <c r="AC35" s="40"/>
+      <c r="AD35" s="40"/>
+      <c r="AE35" s="40"/>
+      <c r="AF35" s="40"/>
+      <c r="AG35" s="40"/>
     </row>
     <row r="36" spans="1:33" ht="15" customHeight="1">
-      <c r="A36" s="21">
+      <c r="A36" s="38">
         <v>15</v>
       </c>
-      <c r="B36" s="81"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="16"/>
-      <c r="P36" s="14"/>
-      <c r="Q36" s="16"/>
-      <c r="R36" s="18"/>
-      <c r="S36" s="14"/>
-      <c r="T36" s="14"/>
-      <c r="U36" s="14"/>
-      <c r="V36" s="14"/>
-      <c r="W36" s="14"/>
-      <c r="X36" s="14"/>
-      <c r="Y36" s="14"/>
-      <c r="Z36" s="14"/>
-      <c r="AA36" s="14"/>
-      <c r="AB36" s="14"/>
-      <c r="AC36" s="14"/>
-      <c r="AD36" s="14"/>
-      <c r="AE36" s="14"/>
-      <c r="AF36" s="14"/>
-      <c r="AG36" s="14"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="64"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="36"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="36"/>
+      <c r="J36" s="36"/>
+      <c r="K36" s="36"/>
+      <c r="L36" s="36"/>
+      <c r="M36" s="36"/>
+      <c r="N36" s="36"/>
+      <c r="O36" s="65"/>
+      <c r="P36" s="36"/>
+      <c r="Q36" s="65"/>
+      <c r="R36" s="64"/>
+      <c r="S36" s="36"/>
+      <c r="T36" s="36"/>
+      <c r="U36" s="36"/>
+      <c r="V36" s="36"/>
+      <c r="W36" s="36"/>
+      <c r="X36" s="36"/>
+      <c r="Y36" s="36"/>
+      <c r="Z36" s="36"/>
+      <c r="AA36" s="36"/>
+      <c r="AB36" s="36"/>
+      <c r="AC36" s="36"/>
+      <c r="AD36" s="36"/>
+      <c r="AE36" s="36"/>
+      <c r="AF36" s="36"/>
+      <c r="AG36" s="36"/>
     </row>
     <row r="37" spans="1:33" ht="15" customHeight="1">
-      <c r="A37" s="22"/>
-      <c r="B37" s="82"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
-      <c r="K37" s="15"/>
-      <c r="L37" s="15"/>
-      <c r="M37" s="15"/>
-      <c r="N37" s="15"/>
-      <c r="O37" s="17"/>
-      <c r="P37" s="15"/>
-      <c r="Q37" s="17"/>
-      <c r="R37" s="19"/>
-      <c r="S37" s="15"/>
-      <c r="T37" s="15"/>
-      <c r="U37" s="15"/>
-      <c r="V37" s="15"/>
-      <c r="W37" s="15"/>
-      <c r="X37" s="15"/>
-      <c r="Y37" s="15"/>
-      <c r="Z37" s="15"/>
-      <c r="AA37" s="15"/>
-      <c r="AB37" s="15"/>
-      <c r="AC37" s="15"/>
-      <c r="AD37" s="15"/>
-      <c r="AE37" s="15"/>
-      <c r="AF37" s="15"/>
-      <c r="AG37" s="15"/>
+      <c r="A37" s="39"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="37"/>
+      <c r="H37" s="37"/>
+      <c r="I37" s="37"/>
+      <c r="J37" s="37"/>
+      <c r="K37" s="37"/>
+      <c r="L37" s="37"/>
+      <c r="M37" s="37"/>
+      <c r="N37" s="37"/>
+      <c r="O37" s="70"/>
+      <c r="P37" s="37"/>
+      <c r="Q37" s="70"/>
+      <c r="R37" s="69"/>
+      <c r="S37" s="37"/>
+      <c r="T37" s="37"/>
+      <c r="U37" s="37"/>
+      <c r="V37" s="37"/>
+      <c r="W37" s="37"/>
+      <c r="X37" s="37"/>
+      <c r="Y37" s="37"/>
+      <c r="Z37" s="37"/>
+      <c r="AA37" s="37"/>
+      <c r="AB37" s="37"/>
+      <c r="AC37" s="37"/>
+      <c r="AD37" s="37"/>
+      <c r="AE37" s="37"/>
+      <c r="AF37" s="37"/>
+      <c r="AG37" s="37"/>
     </row>
     <row r="38" spans="1:33" ht="15" customHeight="1">
-      <c r="A38" s="67"/>
-      <c r="B38" s="68"/>
-      <c r="C38" s="69"/>
-      <c r="D38" s="69"/>
-      <c r="E38" s="69"/>
-      <c r="F38" s="69"/>
-      <c r="G38" s="69"/>
-      <c r="H38" s="69"/>
-      <c r="I38" s="69"/>
-      <c r="J38" s="69"/>
-      <c r="K38" s="69"/>
-      <c r="L38" s="69"/>
-      <c r="M38" s="69"/>
-      <c r="N38" s="69"/>
-      <c r="O38" s="69"/>
-      <c r="P38" s="69"/>
-      <c r="Q38" s="69"/>
-      <c r="R38" s="69"/>
-      <c r="S38" s="69"/>
-      <c r="T38" s="69"/>
-      <c r="U38" s="69"/>
-      <c r="V38" s="69"/>
-      <c r="W38" s="69"/>
-      <c r="X38" s="69"/>
-      <c r="Y38" s="69"/>
-      <c r="Z38" s="69"/>
-      <c r="AA38" s="69"/>
-      <c r="AB38" s="69"/>
-      <c r="AC38" s="69"/>
-      <c r="AD38" s="69"/>
-      <c r="AE38" s="69"/>
-      <c r="AF38" s="69"/>
-      <c r="AG38" s="69"/>
+      <c r="A38" s="16"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="18"/>
+      <c r="P38" s="18"/>
+      <c r="Q38" s="18"/>
+      <c r="R38" s="18"/>
+      <c r="S38" s="18"/>
+      <c r="T38" s="18"/>
+      <c r="U38" s="18"/>
+      <c r="V38" s="18"/>
+      <c r="W38" s="18"/>
+      <c r="X38" s="18"/>
+      <c r="Y38" s="18"/>
+      <c r="Z38" s="18"/>
+      <c r="AA38" s="18"/>
+      <c r="AB38" s="18"/>
+      <c r="AC38" s="18"/>
+      <c r="AD38" s="18"/>
+      <c r="AE38" s="18"/>
+      <c r="AF38" s="18"/>
+      <c r="AG38" s="18"/>
     </row>
     <row r="39" spans="1:33" ht="15" customHeight="1">
-      <c r="A39" s="59" t="s">
+      <c r="A39" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B39" s="64" t="s">
+      <c r="B39" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C39" s="60" t="s">
+      <c r="C39" s="58" t="s">
         <v>60</v>
       </c>
-      <c r="D39" s="60"/>
-      <c r="E39" s="60"/>
-      <c r="F39" s="60"/>
-      <c r="G39" s="60"/>
-      <c r="H39" s="60"/>
-      <c r="I39" s="60" t="s">
+      <c r="D39" s="58"/>
+      <c r="E39" s="58"/>
+      <c r="F39" s="58"/>
+      <c r="G39" s="58"/>
+      <c r="H39" s="58"/>
+      <c r="I39" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="J39" s="60"/>
-      <c r="K39" s="60" t="s">
+      <c r="J39" s="58"/>
+      <c r="K39" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="L39" s="60"/>
-      <c r="M39" s="60" t="s">
+      <c r="L39" s="58"/>
+      <c r="M39" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="N39" s="60"/>
-      <c r="O39" s="60"/>
-      <c r="P39" s="60"/>
-      <c r="Q39" s="60"/>
-      <c r="R39" s="60"/>
-      <c r="S39" s="60"/>
-      <c r="T39" s="60"/>
-      <c r="U39" s="60"/>
-      <c r="V39" s="59"/>
-      <c r="W39" s="62" t="s">
+      <c r="N39" s="58"/>
+      <c r="O39" s="58"/>
+      <c r="P39" s="58"/>
+      <c r="Q39" s="58"/>
+      <c r="R39" s="58"/>
+      <c r="S39" s="58"/>
+      <c r="T39" s="58"/>
+      <c r="U39" s="58"/>
+      <c r="V39" s="11"/>
+      <c r="W39" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="X39" s="66" t="s">
+      <c r="X39" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="Y39" s="66"/>
-      <c r="Z39" s="63" t="s">
+      <c r="Y39" s="34"/>
+      <c r="Z39" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="AA39" s="63"/>
-      <c r="AB39" s="63"/>
-      <c r="AC39" s="63"/>
-      <c r="AD39" s="63"/>
-      <c r="AE39" s="63"/>
-      <c r="AF39" s="63"/>
-      <c r="AG39" s="63"/>
+      <c r="AA39" s="31"/>
+      <c r="AB39" s="31"/>
+      <c r="AC39" s="31"/>
+      <c r="AD39" s="31"/>
+      <c r="AE39" s="31"/>
+      <c r="AF39" s="31"/>
+      <c r="AG39" s="31"/>
     </row>
     <row r="40" spans="1:33" ht="17.25" customHeight="1">
-      <c r="A40" s="59" t="s">
+      <c r="A40" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B40" s="59" t="s">
+      <c r="B40" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="60" t="s">
+      <c r="C40" s="58" t="s">
         <v>61</v>
       </c>
-      <c r="D40" s="60"/>
-      <c r="E40" s="60"/>
-      <c r="F40" s="60"/>
-      <c r="G40" s="60"/>
-      <c r="H40" s="60"/>
-      <c r="I40" s="60" t="s">
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="58"/>
+      <c r="H40" s="58"/>
+      <c r="I40" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="J40" s="60"/>
-      <c r="K40" s="60" t="s">
+      <c r="J40" s="58"/>
+      <c r="K40" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="L40" s="60"/>
-      <c r="M40" s="60" t="s">
+      <c r="L40" s="58"/>
+      <c r="M40" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="N40" s="60"/>
-      <c r="O40" s="60"/>
-      <c r="P40" s="60"/>
-      <c r="Q40" s="60"/>
-      <c r="R40" s="60"/>
-      <c r="S40" s="60"/>
-      <c r="T40" s="60"/>
-      <c r="U40" s="60"/>
-      <c r="V40" s="59"/>
-      <c r="W40" s="59" t="s">
+      <c r="N40" s="58"/>
+      <c r="O40" s="58"/>
+      <c r="P40" s="58"/>
+      <c r="Q40" s="58"/>
+      <c r="R40" s="58"/>
+      <c r="S40" s="58"/>
+      <c r="T40" s="58"/>
+      <c r="U40" s="58"/>
+      <c r="V40" s="11"/>
+      <c r="W40" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="X40" s="66" t="s">
+      <c r="X40" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="Y40" s="66"/>
-      <c r="Z40" s="63" t="s">
+      <c r="Y40" s="34"/>
+      <c r="Z40" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="AA40" s="63"/>
-      <c r="AB40" s="63"/>
-      <c r="AC40" s="63"/>
-      <c r="AD40" s="63"/>
-      <c r="AE40" s="63"/>
-      <c r="AF40" s="63"/>
-      <c r="AG40" s="63"/>
+      <c r="AA40" s="31"/>
+      <c r="AB40" s="31"/>
+      <c r="AC40" s="31"/>
+      <c r="AD40" s="31"/>
+      <c r="AE40" s="31"/>
+      <c r="AF40" s="31"/>
+      <c r="AG40" s="31"/>
     </row>
     <row r="41" spans="1:33" ht="17.25" customHeight="1">
-      <c r="A41" s="59" t="s">
+      <c r="A41" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B41" s="59" t="s">
+      <c r="B41" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C41" s="60" t="s">
+      <c r="C41" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="D41" s="60"/>
-      <c r="E41" s="60"/>
-      <c r="F41" s="60"/>
-      <c r="G41" s="60"/>
-      <c r="H41" s="60"/>
-      <c r="I41" s="60" t="s">
+      <c r="D41" s="58"/>
+      <c r="E41" s="58"/>
+      <c r="F41" s="58"/>
+      <c r="G41" s="58"/>
+      <c r="H41" s="58"/>
+      <c r="I41" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="J41" s="60"/>
-      <c r="K41" s="60" t="s">
+      <c r="J41" s="58"/>
+      <c r="K41" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="L41" s="60"/>
-      <c r="M41" s="60" t="s">
+      <c r="L41" s="58"/>
+      <c r="M41" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="N41" s="60"/>
-      <c r="O41" s="60"/>
-      <c r="P41" s="60"/>
-      <c r="Q41" s="60"/>
-      <c r="R41" s="60"/>
-      <c r="S41" s="60"/>
-      <c r="T41" s="60"/>
-      <c r="U41" s="60"/>
-      <c r="V41" s="59"/>
-      <c r="W41" s="59" t="s">
+      <c r="N41" s="58"/>
+      <c r="O41" s="58"/>
+      <c r="P41" s="58"/>
+      <c r="Q41" s="58"/>
+      <c r="R41" s="58"/>
+      <c r="S41" s="58"/>
+      <c r="T41" s="58"/>
+      <c r="U41" s="58"/>
+      <c r="V41" s="11"/>
+      <c r="W41" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="X41" s="66" t="s">
+      <c r="X41" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="Y41" s="66"/>
-      <c r="Z41" s="63" t="s">
+      <c r="Y41" s="34"/>
+      <c r="Z41" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="AA41" s="63"/>
-      <c r="AB41" s="63"/>
-      <c r="AC41" s="63"/>
-      <c r="AD41" s="63"/>
-      <c r="AE41" s="63"/>
-      <c r="AF41" s="63"/>
-      <c r="AG41" s="63"/>
+      <c r="AA41" s="31"/>
+      <c r="AB41" s="31"/>
+      <c r="AC41" s="31"/>
+      <c r="AD41" s="31"/>
+      <c r="AE41" s="31"/>
+      <c r="AF41" s="31"/>
+      <c r="AG41" s="31"/>
     </row>
     <row r="42" spans="1:33" ht="17.25" customHeight="1">
-      <c r="A42" s="59" t="s">
+      <c r="A42" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B42" s="59" t="s">
+      <c r="B42" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C42" s="60" t="s">
+      <c r="C42" s="58" t="s">
         <v>63</v>
       </c>
-      <c r="D42" s="60"/>
-      <c r="E42" s="60"/>
-      <c r="F42" s="60"/>
-      <c r="G42" s="60"/>
-      <c r="H42" s="60"/>
-      <c r="I42" s="66"/>
-      <c r="J42" s="66"/>
-      <c r="K42" s="66"/>
-      <c r="L42" s="66"/>
-      <c r="M42" s="66"/>
-      <c r="N42" s="66"/>
-      <c r="O42" s="66"/>
-      <c r="P42" s="66"/>
-      <c r="Q42" s="66"/>
-      <c r="R42" s="66"/>
-      <c r="S42" s="66"/>
-      <c r="T42" s="66"/>
-      <c r="U42" s="66"/>
-      <c r="V42" s="65"/>
-      <c r="W42" s="59" t="s">
+      <c r="D42" s="58"/>
+      <c r="E42" s="58"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="58"/>
+      <c r="H42" s="58"/>
+      <c r="I42" s="34"/>
+      <c r="J42" s="34"/>
+      <c r="K42" s="34"/>
+      <c r="L42" s="34"/>
+      <c r="M42" s="34"/>
+      <c r="N42" s="34"/>
+      <c r="O42" s="34"/>
+      <c r="P42" s="34"/>
+      <c r="Q42" s="34"/>
+      <c r="R42" s="34"/>
+      <c r="S42" s="34"/>
+      <c r="T42" s="34"/>
+      <c r="U42" s="34"/>
+      <c r="V42" s="15"/>
+      <c r="W42" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="X42" s="66" t="s">
+      <c r="X42" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="Y42" s="66"/>
-      <c r="Z42" s="63" t="s">
+      <c r="Y42" s="34"/>
+      <c r="Z42" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="AA42" s="63"/>
-      <c r="AB42" s="63"/>
-      <c r="AC42" s="63"/>
-      <c r="AD42" s="63"/>
-      <c r="AE42" s="63"/>
-      <c r="AF42" s="63"/>
-      <c r="AG42" s="63"/>
+      <c r="AA42" s="31"/>
+      <c r="AB42" s="31"/>
+      <c r="AC42" s="31"/>
+      <c r="AD42" s="31"/>
+      <c r="AE42" s="31"/>
+      <c r="AF42" s="31"/>
+      <c r="AG42" s="31"/>
     </row>
     <row r="43" spans="1:33" ht="17.25" customHeight="1">
-      <c r="A43" s="59" t="s">
+      <c r="A43" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B43" s="59" t="s">
+      <c r="B43" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C43" s="66" t="s">
+      <c r="C43" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="D43" s="66"/>
-      <c r="E43" s="66"/>
-      <c r="F43" s="66"/>
-      <c r="G43" s="66"/>
-      <c r="H43" s="66"/>
-      <c r="I43" s="70"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="66"/>
-      <c r="L43" s="63"/>
-      <c r="M43" s="63"/>
-      <c r="N43" s="63"/>
-      <c r="O43" s="63"/>
-      <c r="P43" s="63"/>
-      <c r="Q43" s="63"/>
-      <c r="R43" s="63"/>
-      <c r="S43" s="63"/>
-      <c r="T43" s="63"/>
-      <c r="U43" s="59"/>
-      <c r="V43" s="59"/>
-      <c r="W43" s="59" t="s">
+      <c r="D43" s="34"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="34"/>
+      <c r="K43" s="34"/>
+      <c r="L43" s="31"/>
+      <c r="M43" s="31"/>
+      <c r="N43" s="31"/>
+      <c r="O43" s="31"/>
+      <c r="P43" s="31"/>
+      <c r="Q43" s="31"/>
+      <c r="R43" s="31"/>
+      <c r="S43" s="31"/>
+      <c r="T43" s="31"/>
+      <c r="U43" s="11"/>
+      <c r="V43" s="11"/>
+      <c r="W43" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="X43" s="66" t="s">
+      <c r="X43" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="Y43" s="66"/>
-      <c r="Z43" s="63" t="s">
+      <c r="Y43" s="34"/>
+      <c r="Z43" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="AA43" s="63"/>
-      <c r="AB43" s="63"/>
-      <c r="AC43" s="63"/>
-      <c r="AD43" s="63"/>
-      <c r="AE43" s="63"/>
-      <c r="AF43" s="63"/>
-      <c r="AG43" s="63"/>
+      <c r="AA43" s="31"/>
+      <c r="AB43" s="31"/>
+      <c r="AC43" s="31"/>
+      <c r="AD43" s="31"/>
+      <c r="AE43" s="31"/>
+      <c r="AF43" s="31"/>
+      <c r="AG43" s="31"/>
     </row>
     <row r="44" spans="1:33" ht="17.25" customHeight="1">
-      <c r="A44" s="59"/>
-      <c r="B44" s="71" t="s">
+      <c r="A44" s="11"/>
+      <c r="B44" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="59"/>
-      <c r="D44" s="59"/>
-      <c r="E44" s="59"/>
-      <c r="F44" s="59"/>
-      <c r="G44" s="59"/>
-      <c r="H44" s="59"/>
-      <c r="I44" s="59"/>
-      <c r="J44" s="65"/>
-      <c r="K44" s="65"/>
-      <c r="L44" s="59"/>
-      <c r="M44" s="72" t="s">
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="15"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="N44" s="72"/>
-      <c r="O44" s="72"/>
-      <c r="P44" s="59"/>
-      <c r="Q44" s="59"/>
-      <c r="R44" s="59"/>
-      <c r="S44" s="59"/>
-      <c r="T44" s="59"/>
-      <c r="U44" s="59"/>
-      <c r="V44" s="59"/>
-      <c r="W44" s="59" t="s">
+      <c r="N44" s="35"/>
+      <c r="O44" s="35"/>
+      <c r="P44" s="11"/>
+      <c r="Q44" s="11"/>
+      <c r="R44" s="11"/>
+      <c r="S44" s="11"/>
+      <c r="T44" s="11"/>
+      <c r="U44" s="11"/>
+      <c r="V44" s="11"/>
+      <c r="W44" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="X44" s="66" t="s">
+      <c r="X44" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="Y44" s="66"/>
-      <c r="Z44" s="63" t="s">
+      <c r="Y44" s="34"/>
+      <c r="Z44" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="AA44" s="63"/>
-      <c r="AB44" s="63"/>
-      <c r="AC44" s="63"/>
-      <c r="AD44" s="63"/>
-      <c r="AE44" s="63"/>
-      <c r="AF44" s="63"/>
-      <c r="AG44" s="63"/>
+      <c r="AA44" s="31"/>
+      <c r="AB44" s="31"/>
+      <c r="AC44" s="31"/>
+      <c r="AD44" s="31"/>
+      <c r="AE44" s="31"/>
+      <c r="AF44" s="31"/>
+      <c r="AG44" s="31"/>
     </row>
     <row r="45" spans="1:33" ht="17.25" customHeight="1">
-      <c r="A45" s="59"/>
-      <c r="B45" s="65" t="s">
+      <c r="A45" s="11"/>
+      <c r="B45" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C45" s="73" t="s">
+      <c r="C45" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="D45" s="73"/>
-      <c r="E45" s="73"/>
-      <c r="F45" s="73"/>
-      <c r="G45" s="73"/>
-      <c r="H45" s="73"/>
-      <c r="I45" s="73"/>
-      <c r="J45" s="73"/>
-      <c r="K45" s="73"/>
-      <c r="L45" s="63" t="s">
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="30"/>
+      <c r="I45" s="30"/>
+      <c r="J45" s="30"/>
+      <c r="K45" s="30"/>
+      <c r="L45" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M45" s="63"/>
-      <c r="N45" s="73"/>
-      <c r="O45" s="73"/>
-      <c r="P45" s="73"/>
-      <c r="Q45" s="73"/>
-      <c r="R45" s="73"/>
-      <c r="S45" s="73"/>
-      <c r="T45" s="73"/>
-      <c r="U45" s="73"/>
-      <c r="V45" s="73"/>
-      <c r="W45" s="59" t="s">
+      <c r="M45" s="31"/>
+      <c r="N45" s="30"/>
+      <c r="O45" s="30"/>
+      <c r="P45" s="30"/>
+      <c r="Q45" s="30"/>
+      <c r="R45" s="30"/>
+      <c r="S45" s="30"/>
+      <c r="T45" s="30"/>
+      <c r="U45" s="30"/>
+      <c r="V45" s="30"/>
+      <c r="W45" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="X45" s="66" t="s">
+      <c r="X45" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="Y45" s="66"/>
-      <c r="Z45" s="63" t="s">
+      <c r="Y45" s="34"/>
+      <c r="Z45" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="AA45" s="63"/>
-      <c r="AB45" s="63"/>
-      <c r="AC45" s="63"/>
-      <c r="AD45" s="63"/>
-      <c r="AE45" s="63"/>
-      <c r="AF45" s="63"/>
-      <c r="AG45" s="63"/>
+      <c r="AA45" s="31"/>
+      <c r="AB45" s="31"/>
+      <c r="AC45" s="31"/>
+      <c r="AD45" s="31"/>
+      <c r="AE45" s="31"/>
+      <c r="AF45" s="31"/>
+      <c r="AG45" s="31"/>
     </row>
     <row r="46" spans="1:33" ht="17.25" customHeight="1">
-      <c r="A46" s="59"/>
-      <c r="B46" s="65" t="s">
+      <c r="A46" s="11"/>
+      <c r="B46" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C46" s="73"/>
-      <c r="D46" s="73"/>
-      <c r="E46" s="73"/>
-      <c r="F46" s="73"/>
-      <c r="G46" s="73"/>
-      <c r="H46" s="73"/>
-      <c r="I46" s="73"/>
-      <c r="J46" s="73"/>
-      <c r="K46" s="73"/>
-      <c r="L46" s="63" t="s">
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="M46" s="63"/>
-      <c r="N46" s="73"/>
-      <c r="O46" s="73"/>
-      <c r="P46" s="73"/>
-      <c r="Q46" s="73"/>
-      <c r="R46" s="73"/>
-      <c r="S46" s="73"/>
-      <c r="T46" s="73"/>
-      <c r="U46" s="73"/>
-      <c r="V46" s="73"/>
-      <c r="W46" s="59"/>
-      <c r="X46" s="59"/>
-      <c r="Y46" s="59"/>
-      <c r="Z46" s="59"/>
-      <c r="AA46" s="59"/>
-      <c r="AB46" s="66"/>
-      <c r="AC46" s="66"/>
-      <c r="AD46" s="66"/>
-      <c r="AE46" s="66"/>
-      <c r="AF46" s="66"/>
-      <c r="AG46" s="66"/>
+      <c r="M46" s="31"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
+      <c r="R46" s="30"/>
+      <c r="S46" s="30"/>
+      <c r="T46" s="30"/>
+      <c r="U46" s="30"/>
+      <c r="V46" s="30"/>
+      <c r="W46" s="11"/>
+      <c r="X46" s="11"/>
+      <c r="Y46" s="11"/>
+      <c r="Z46" s="11"/>
+      <c r="AA46" s="11"/>
+      <c r="AB46" s="34"/>
+      <c r="AC46" s="34"/>
+      <c r="AD46" s="34"/>
+      <c r="AE46" s="34"/>
+      <c r="AF46" s="34"/>
+      <c r="AG46" s="34"/>
     </row>
     <row r="47" spans="1:33" ht="17.25" customHeight="1">
-      <c r="A47" s="59"/>
-      <c r="B47" s="65" t="s">
+      <c r="A47" s="11"/>
+      <c r="B47" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C47" s="73"/>
-      <c r="D47" s="73"/>
-      <c r="E47" s="73"/>
-      <c r="F47" s="73"/>
-      <c r="G47" s="73"/>
-      <c r="H47" s="73"/>
-      <c r="I47" s="73"/>
-      <c r="J47" s="73"/>
-      <c r="K47" s="73"/>
-      <c r="L47" s="63" t="s">
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="30"/>
+      <c r="I47" s="30"/>
+      <c r="J47" s="30"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M47" s="63"/>
-      <c r="N47" s="74"/>
-      <c r="O47" s="74"/>
-      <c r="P47" s="74"/>
-      <c r="Q47" s="74"/>
-      <c r="R47" s="74"/>
-      <c r="S47" s="74"/>
-      <c r="T47" s="74"/>
-      <c r="U47" s="74"/>
-      <c r="V47" s="74"/>
-      <c r="W47" s="59"/>
-      <c r="X47" s="59"/>
-      <c r="Y47" s="59"/>
-      <c r="Z47" s="59"/>
-      <c r="AA47" s="59"/>
-      <c r="AB47" s="66"/>
-      <c r="AC47" s="66"/>
-      <c r="AD47" s="66"/>
-      <c r="AE47" s="66"/>
-      <c r="AF47" s="66"/>
-      <c r="AG47" s="66"/>
+      <c r="M47" s="31"/>
+      <c r="N47" s="32"/>
+      <c r="O47" s="32"/>
+      <c r="P47" s="32"/>
+      <c r="Q47" s="32"/>
+      <c r="R47" s="32"/>
+      <c r="S47" s="32"/>
+      <c r="T47" s="32"/>
+      <c r="U47" s="32"/>
+      <c r="V47" s="32"/>
+      <c r="W47" s="11"/>
+      <c r="X47" s="11"/>
+      <c r="Y47" s="11"/>
+      <c r="Z47" s="11"/>
+      <c r="AA47" s="11"/>
+      <c r="AB47" s="34"/>
+      <c r="AC47" s="34"/>
+      <c r="AD47" s="34"/>
+      <c r="AE47" s="34"/>
+      <c r="AF47" s="34"/>
+      <c r="AG47" s="34"/>
     </row>
     <row r="48" spans="1:33" ht="17.25" customHeight="1">
-      <c r="A48" s="59"/>
-      <c r="B48" s="65" t="s">
+      <c r="A48" s="11"/>
+      <c r="B48" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C48" s="73"/>
-      <c r="D48" s="73"/>
-      <c r="E48" s="73"/>
-      <c r="F48" s="73"/>
-      <c r="G48" s="73"/>
-      <c r="H48" s="73"/>
-      <c r="I48" s="73"/>
-      <c r="J48" s="73"/>
-      <c r="K48" s="73"/>
-      <c r="L48" s="63" t="s">
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
+      <c r="I48" s="30"/>
+      <c r="J48" s="30"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M48" s="63"/>
-      <c r="N48" s="74"/>
-      <c r="O48" s="74"/>
-      <c r="P48" s="74"/>
-      <c r="Q48" s="74"/>
-      <c r="R48" s="74"/>
-      <c r="S48" s="74"/>
-      <c r="T48" s="74"/>
-      <c r="U48" s="74"/>
-      <c r="V48" s="74"/>
-      <c r="W48" s="59"/>
-      <c r="X48" s="59"/>
-      <c r="Y48" s="59"/>
-      <c r="Z48" s="59"/>
-      <c r="AA48" s="75" t="s">
+      <c r="M48" s="31"/>
+      <c r="N48" s="32"/>
+      <c r="O48" s="32"/>
+      <c r="P48" s="32"/>
+      <c r="Q48" s="32"/>
+      <c r="R48" s="32"/>
+      <c r="S48" s="32"/>
+      <c r="T48" s="32"/>
+      <c r="U48" s="32"/>
+      <c r="V48" s="32"/>
+      <c r="W48" s="11"/>
+      <c r="X48" s="11"/>
+      <c r="Y48" s="11"/>
+      <c r="Z48" s="11"/>
+      <c r="AA48" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="AB48" s="75"/>
-      <c r="AC48" s="75"/>
-      <c r="AD48" s="75"/>
-      <c r="AE48" s="75"/>
-      <c r="AF48" s="75"/>
-      <c r="AG48" s="75"/>
+      <c r="AB48" s="33"/>
+      <c r="AC48" s="33"/>
+      <c r="AD48" s="33"/>
+      <c r="AE48" s="33"/>
+      <c r="AF48" s="33"/>
+      <c r="AG48" s="33"/>
     </row>
     <row r="49" spans="1:40" ht="17.25" customHeight="1">
-      <c r="A49" s="59"/>
-      <c r="B49" s="61" t="s">
+      <c r="A49" s="11"/>
+      <c r="B49" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C49" s="73"/>
-      <c r="D49" s="73"/>
-      <c r="E49" s="73"/>
-      <c r="F49" s="73"/>
-      <c r="G49" s="73"/>
-      <c r="H49" s="73"/>
-      <c r="I49" s="73"/>
-      <c r="J49" s="73"/>
-      <c r="K49" s="73"/>
-      <c r="L49" s="63" t="s">
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M49" s="63"/>
-      <c r="N49" s="74"/>
-      <c r="O49" s="74"/>
-      <c r="P49" s="74"/>
-      <c r="Q49" s="74"/>
-      <c r="R49" s="74"/>
-      <c r="S49" s="74"/>
-      <c r="T49" s="74"/>
-      <c r="U49" s="74"/>
-      <c r="V49" s="74"/>
-      <c r="W49" s="59"/>
-      <c r="X49" s="59"/>
-      <c r="Y49" s="59"/>
-      <c r="Z49" s="59"/>
-      <c r="AA49" s="75" t="s">
+      <c r="M49" s="31"/>
+      <c r="N49" s="32"/>
+      <c r="O49" s="32"/>
+      <c r="P49" s="32"/>
+      <c r="Q49" s="32"/>
+      <c r="R49" s="32"/>
+      <c r="S49" s="32"/>
+      <c r="T49" s="32"/>
+      <c r="U49" s="32"/>
+      <c r="V49" s="32"/>
+      <c r="W49" s="11"/>
+      <c r="X49" s="11"/>
+      <c r="Y49" s="11"/>
+      <c r="Z49" s="11"/>
+      <c r="AA49" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="AB49" s="75"/>
-      <c r="AC49" s="75"/>
-      <c r="AD49" s="75"/>
-      <c r="AE49" s="75"/>
-      <c r="AF49" s="75"/>
-      <c r="AG49" s="75"/>
+      <c r="AB49" s="33"/>
+      <c r="AC49" s="33"/>
+      <c r="AD49" s="33"/>
+      <c r="AE49" s="33"/>
+      <c r="AF49" s="33"/>
+      <c r="AG49" s="33"/>
     </row>
     <row r="50" spans="1:40" ht="17.25" customHeight="1">
-      <c r="A50" s="59"/>
-      <c r="B50" s="76" t="s">
+      <c r="A50" s="11"/>
+      <c r="B50" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="C50" s="76"/>
-      <c r="D50" s="76"/>
-      <c r="E50" s="76"/>
-      <c r="F50" s="76"/>
-      <c r="G50" s="76"/>
-      <c r="H50" s="76"/>
-      <c r="I50" s="76"/>
-      <c r="J50" s="76"/>
-      <c r="K50" s="76"/>
-      <c r="L50" s="76"/>
-      <c r="M50" s="76"/>
-      <c r="N50" s="76"/>
-      <c r="O50" s="76"/>
-      <c r="P50" s="76"/>
-      <c r="Q50" s="76"/>
-      <c r="R50" s="76"/>
-      <c r="S50" s="76"/>
-      <c r="T50" s="76"/>
-      <c r="U50" s="76"/>
-      <c r="V50" s="59"/>
-      <c r="W50" s="59"/>
-      <c r="X50" s="59"/>
-      <c r="Y50" s="59"/>
-      <c r="Z50" s="59"/>
-      <c r="AA50" s="77" t="s">
+      <c r="C50" s="26"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="26"/>
+      <c r="G50" s="26"/>
+      <c r="H50" s="26"/>
+      <c r="I50" s="26"/>
+      <c r="J50" s="26"/>
+      <c r="K50" s="26"/>
+      <c r="L50" s="26"/>
+      <c r="M50" s="26"/>
+      <c r="N50" s="26"/>
+      <c r="O50" s="26"/>
+      <c r="P50" s="26"/>
+      <c r="Q50" s="26"/>
+      <c r="R50" s="26"/>
+      <c r="S50" s="26"/>
+      <c r="T50" s="26"/>
+      <c r="U50" s="26"/>
+      <c r="V50" s="11"/>
+      <c r="W50" s="11"/>
+      <c r="X50" s="11"/>
+      <c r="Y50" s="11"/>
+      <c r="Z50" s="11"/>
+      <c r="AA50" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="AB50" s="77"/>
-      <c r="AC50" s="77"/>
-      <c r="AD50" s="77"/>
-      <c r="AE50" s="77"/>
-      <c r="AF50" s="77"/>
-      <c r="AG50" s="77"/>
+      <c r="AB50" s="27"/>
+      <c r="AC50" s="27"/>
+      <c r="AD50" s="27"/>
+      <c r="AE50" s="27"/>
+      <c r="AF50" s="27"/>
+      <c r="AG50" s="27"/>
     </row>
     <row r="51" spans="1:40" s="10" customFormat="1" ht="17.25" customHeight="1">
       <c r="A51" s="9"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="11"/>
-      <c r="I51" s="11"/>
-      <c r="J51" s="11"/>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
-      <c r="N51" s="11"/>
-      <c r="O51" s="11"/>
-      <c r="P51" s="11"/>
-      <c r="Q51" s="11"/>
-      <c r="R51" s="11"/>
-      <c r="S51" s="11"/>
-      <c r="T51" s="11"/>
-      <c r="U51" s="11"/>
+      <c r="B51" s="28"/>
+      <c r="C51" s="28"/>
+      <c r="D51" s="28"/>
+      <c r="E51" s="28"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="28"/>
+      <c r="H51" s="28"/>
+      <c r="I51" s="28"/>
+      <c r="J51" s="28"/>
+      <c r="K51" s="28"/>
+      <c r="L51" s="28"/>
+      <c r="M51" s="28"/>
+      <c r="N51" s="28"/>
+      <c r="O51" s="28"/>
+      <c r="P51" s="28"/>
+      <c r="Q51" s="28"/>
+      <c r="R51" s="28"/>
+      <c r="S51" s="28"/>
+      <c r="T51" s="28"/>
+      <c r="U51" s="28"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
       <c r="X51" s="9"/>
       <c r="Y51" s="9"/>
       <c r="Z51" s="9"/>
-      <c r="AA51" s="12" t="s">
+      <c r="AA51" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="AB51" s="12"/>
-      <c r="AC51" s="12"/>
-      <c r="AD51" s="12"/>
-      <c r="AE51" s="12"/>
-      <c r="AF51" s="12"/>
-      <c r="AG51" s="12"/>
+      <c r="AB51" s="29"/>
+      <c r="AC51" s="29"/>
+      <c r="AD51" s="29"/>
+      <c r="AE51" s="29"/>
+      <c r="AF51" s="29"/>
+      <c r="AG51" s="29"/>
       <c r="AH51" s="1"/>
       <c r="AI51" s="1"/>
       <c r="AJ51" s="1"/>
@@ -4215,33 +4151,33 @@
       <c r="AN51" s="1"/>
     </row>
     <row r="52" spans="1:40" s="10" customFormat="1" ht="19.5" customHeight="1">
-      <c r="B52" s="11"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="11"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="11"/>
-      <c r="I52" s="11"/>
-      <c r="J52" s="11"/>
-      <c r="K52" s="11"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="11"/>
-      <c r="O52" s="11"/>
-      <c r="P52" s="11"/>
-      <c r="Q52" s="11"/>
-      <c r="R52" s="11"/>
-      <c r="S52" s="11"/>
-      <c r="T52" s="11"/>
-      <c r="U52" s="11"/>
-      <c r="AA52" s="12"/>
-      <c r="AB52" s="12"/>
-      <c r="AC52" s="12"/>
-      <c r="AD52" s="12"/>
-      <c r="AE52" s="12"/>
-      <c r="AF52" s="12"/>
-      <c r="AG52" s="12"/>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="28"/>
+      <c r="L52" s="28"/>
+      <c r="M52" s="28"/>
+      <c r="N52" s="28"/>
+      <c r="O52" s="28"/>
+      <c r="P52" s="28"/>
+      <c r="Q52" s="28"/>
+      <c r="R52" s="28"/>
+      <c r="S52" s="28"/>
+      <c r="T52" s="28"/>
+      <c r="U52" s="28"/>
+      <c r="AA52" s="29"/>
+      <c r="AB52" s="29"/>
+      <c r="AC52" s="29"/>
+      <c r="AD52" s="29"/>
+      <c r="AE52" s="29"/>
+      <c r="AF52" s="29"/>
+      <c r="AG52" s="29"/>
       <c r="AH52" s="1"/>
       <c r="AI52" s="1"/>
       <c r="AJ52" s="1"/>
@@ -4295,6 +4231,16 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="Q10:Q11"/>
+    <mergeCell ref="R10:R11"/>
+    <mergeCell ref="S10:S11"/>
     <mergeCell ref="A1:AG1"/>
     <mergeCell ref="A3:AG3"/>
     <mergeCell ref="H4:J4"/>
@@ -4315,12 +4261,6 @@
     <mergeCell ref="AE8:AE9"/>
     <mergeCell ref="AF8:AF9"/>
     <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
     <mergeCell ref="X8:X9"/>
     <mergeCell ref="Y8:Y9"/>
     <mergeCell ref="Z8:Z9"/>
@@ -4335,10 +4275,6 @@
     <mergeCell ref="W8:W9"/>
     <mergeCell ref="L8:L9"/>
     <mergeCell ref="M8:M9"/>
-    <mergeCell ref="P10:P11"/>
-    <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="R10:R11"/>
-    <mergeCell ref="S10:S11"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="J10:J11"/>
@@ -4378,12 +4314,15 @@
     <mergeCell ref="Y12:Y13"/>
     <mergeCell ref="Z12:Z13"/>
     <mergeCell ref="AA12:AA13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="O12:O13"/>
+    <mergeCell ref="P14:P15"/>
+    <mergeCell ref="Q14:Q15"/>
+    <mergeCell ref="R14:R15"/>
     <mergeCell ref="AB12:AB13"/>
     <mergeCell ref="AC12:AC13"/>
     <mergeCell ref="AD12:AD13"/>
@@ -4393,24 +4332,19 @@
     <mergeCell ref="S12:S13"/>
     <mergeCell ref="T12:T13"/>
     <mergeCell ref="U12:U13"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="N12:N13"/>
-    <mergeCell ref="O12:O13"/>
-    <mergeCell ref="P14:P15"/>
-    <mergeCell ref="Q14:Q15"/>
-    <mergeCell ref="R14:R15"/>
-    <mergeCell ref="S14:S15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:M15"/>
     <mergeCell ref="AF14:AF15"/>
     <mergeCell ref="AG14:AG15"/>
+    <mergeCell ref="AA14:AA15"/>
+    <mergeCell ref="AB14:AB15"/>
+    <mergeCell ref="AC14:AC15"/>
+    <mergeCell ref="AD14:AD15"/>
+    <mergeCell ref="AE14:AE15"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="D16:D17"/>
@@ -4420,11 +4354,6 @@
     <mergeCell ref="H16:H17"/>
     <mergeCell ref="I16:I17"/>
     <mergeCell ref="Z14:Z15"/>
-    <mergeCell ref="AA14:AA15"/>
-    <mergeCell ref="AB14:AB15"/>
-    <mergeCell ref="AC14:AC15"/>
-    <mergeCell ref="AD14:AD15"/>
-    <mergeCell ref="AE14:AE15"/>
     <mergeCell ref="T14:T15"/>
     <mergeCell ref="U14:U15"/>
     <mergeCell ref="V14:V15"/>
@@ -4433,6 +4362,13 @@
     <mergeCell ref="Y14:Y15"/>
     <mergeCell ref="N14:N15"/>
     <mergeCell ref="O14:O15"/>
+    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M14:M15"/>
     <mergeCell ref="AE16:AE17"/>
     <mergeCell ref="AF16:AF17"/>
     <mergeCell ref="AG16:AG17"/>
@@ -4442,12 +4378,15 @@
     <mergeCell ref="Y16:Y17"/>
     <mergeCell ref="Z16:Z17"/>
     <mergeCell ref="AA16:AA17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="O16:O17"/>
+    <mergeCell ref="P18:P19"/>
+    <mergeCell ref="Q18:Q19"/>
+    <mergeCell ref="R18:R19"/>
     <mergeCell ref="AB16:AB17"/>
     <mergeCell ref="AC16:AC17"/>
     <mergeCell ref="AD16:AD17"/>
@@ -4457,24 +4396,19 @@
     <mergeCell ref="S16:S17"/>
     <mergeCell ref="T16:T17"/>
     <mergeCell ref="U16:U17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="L16:L17"/>
-    <mergeCell ref="M16:M17"/>
-    <mergeCell ref="N16:N17"/>
-    <mergeCell ref="O16:O17"/>
-    <mergeCell ref="P18:P19"/>
-    <mergeCell ref="Q18:Q19"/>
-    <mergeCell ref="R18:R19"/>
-    <mergeCell ref="S18:S19"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="M18:M19"/>
     <mergeCell ref="AF18:AF19"/>
     <mergeCell ref="AG18:AG19"/>
+    <mergeCell ref="AA18:AA19"/>
+    <mergeCell ref="AB18:AB19"/>
+    <mergeCell ref="AC18:AC19"/>
+    <mergeCell ref="AD18:AD19"/>
+    <mergeCell ref="AE18:AE19"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="G18:G19"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="D20:D21"/>
@@ -4484,11 +4418,6 @@
     <mergeCell ref="H20:H21"/>
     <mergeCell ref="I20:I21"/>
     <mergeCell ref="Z18:Z19"/>
-    <mergeCell ref="AA18:AA19"/>
-    <mergeCell ref="AB18:AB19"/>
-    <mergeCell ref="AC18:AC19"/>
-    <mergeCell ref="AD18:AD19"/>
-    <mergeCell ref="AE18:AE19"/>
     <mergeCell ref="T18:T19"/>
     <mergeCell ref="U18:U19"/>
     <mergeCell ref="V18:V19"/>
@@ -4497,6 +4426,13 @@
     <mergeCell ref="Y18:Y19"/>
     <mergeCell ref="N18:N19"/>
     <mergeCell ref="O18:O19"/>
+    <mergeCell ref="S18:S19"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="M18:M19"/>
     <mergeCell ref="AE20:AE21"/>
     <mergeCell ref="AF20:AF21"/>
     <mergeCell ref="AG20:AG21"/>
@@ -4506,12 +4442,15 @@
     <mergeCell ref="Y20:Y21"/>
     <mergeCell ref="Z20:Z21"/>
     <mergeCell ref="AA20:AA21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="L20:L21"/>
+    <mergeCell ref="M20:M21"/>
+    <mergeCell ref="N20:N21"/>
+    <mergeCell ref="O20:O21"/>
+    <mergeCell ref="P22:P23"/>
+    <mergeCell ref="Q22:Q23"/>
+    <mergeCell ref="R22:R23"/>
     <mergeCell ref="AB20:AB21"/>
     <mergeCell ref="AC20:AC21"/>
     <mergeCell ref="AD20:AD21"/>
@@ -4521,24 +4460,19 @@
     <mergeCell ref="S20:S21"/>
     <mergeCell ref="T20:T21"/>
     <mergeCell ref="U20:U21"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="L20:L21"/>
-    <mergeCell ref="M20:M21"/>
-    <mergeCell ref="N20:N21"/>
-    <mergeCell ref="O20:O21"/>
-    <mergeCell ref="P22:P23"/>
-    <mergeCell ref="Q22:Q23"/>
-    <mergeCell ref="R22:R23"/>
-    <mergeCell ref="S22:S23"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="K22:K23"/>
-    <mergeCell ref="L22:L23"/>
-    <mergeCell ref="M22:M23"/>
     <mergeCell ref="AF22:AF23"/>
     <mergeCell ref="AG22:AG23"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="AB22:AB23"/>
+    <mergeCell ref="AC22:AC23"/>
+    <mergeCell ref="AD22:AD23"/>
+    <mergeCell ref="AE22:AE23"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="G22:G23"/>
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="C24:C25"/>
     <mergeCell ref="D24:D25"/>
@@ -4548,11 +4482,6 @@
     <mergeCell ref="H24:H25"/>
     <mergeCell ref="I24:I25"/>
     <mergeCell ref="Z22:Z23"/>
-    <mergeCell ref="AA22:AA23"/>
-    <mergeCell ref="AB22:AB23"/>
-    <mergeCell ref="AC22:AC23"/>
-    <mergeCell ref="AD22:AD23"/>
-    <mergeCell ref="AE22:AE23"/>
     <mergeCell ref="T22:T23"/>
     <mergeCell ref="U22:U23"/>
     <mergeCell ref="V22:V23"/>
@@ -4561,6 +4490,13 @@
     <mergeCell ref="Y22:Y23"/>
     <mergeCell ref="N22:N23"/>
     <mergeCell ref="O22:O23"/>
+    <mergeCell ref="S22:S23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="M22:M23"/>
     <mergeCell ref="AE24:AE25"/>
     <mergeCell ref="AF24:AF25"/>
     <mergeCell ref="AG24:AG25"/>
@@ -4570,12 +4506,15 @@
     <mergeCell ref="Y24:Y25"/>
     <mergeCell ref="Z24:Z25"/>
     <mergeCell ref="AA24:AA25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="K24:K25"/>
+    <mergeCell ref="L24:L25"/>
+    <mergeCell ref="M24:M25"/>
+    <mergeCell ref="N24:N25"/>
+    <mergeCell ref="O24:O25"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="Q26:Q27"/>
+    <mergeCell ref="R26:R27"/>
     <mergeCell ref="AB24:AB25"/>
     <mergeCell ref="AC24:AC25"/>
     <mergeCell ref="AD24:AD25"/>
@@ -4585,24 +4524,19 @@
     <mergeCell ref="S24:S25"/>
     <mergeCell ref="T24:T25"/>
     <mergeCell ref="U24:U25"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="K24:K25"/>
-    <mergeCell ref="L24:L25"/>
-    <mergeCell ref="M24:M25"/>
-    <mergeCell ref="N24:N25"/>
-    <mergeCell ref="O24:O25"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="Q26:Q27"/>
-    <mergeCell ref="R26:R27"/>
-    <mergeCell ref="S26:S27"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="K26:K27"/>
-    <mergeCell ref="L26:L27"/>
-    <mergeCell ref="M26:M27"/>
     <mergeCell ref="AF26:AF27"/>
     <mergeCell ref="AG26:AG27"/>
+    <mergeCell ref="AA26:AA27"/>
+    <mergeCell ref="AB26:AB27"/>
+    <mergeCell ref="AC26:AC27"/>
+    <mergeCell ref="AD26:AD27"/>
+    <mergeCell ref="AE26:AE27"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="G26:G27"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="D28:D29"/>
@@ -4612,11 +4546,6 @@
     <mergeCell ref="H28:H29"/>
     <mergeCell ref="I28:I29"/>
     <mergeCell ref="Z26:Z27"/>
-    <mergeCell ref="AA26:AA27"/>
-    <mergeCell ref="AB26:AB27"/>
-    <mergeCell ref="AC26:AC27"/>
-    <mergeCell ref="AD26:AD27"/>
-    <mergeCell ref="AE26:AE27"/>
     <mergeCell ref="T26:T27"/>
     <mergeCell ref="U26:U27"/>
     <mergeCell ref="V26:V27"/>
@@ -4625,6 +4554,13 @@
     <mergeCell ref="Y26:Y27"/>
     <mergeCell ref="N26:N27"/>
     <mergeCell ref="O26:O27"/>
+    <mergeCell ref="S26:S27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="K26:K27"/>
+    <mergeCell ref="L26:L27"/>
+    <mergeCell ref="M26:M27"/>
     <mergeCell ref="AE28:AE29"/>
     <mergeCell ref="AF28:AF29"/>
     <mergeCell ref="AG28:AG29"/>
@@ -4634,12 +4570,15 @@
     <mergeCell ref="Y28:Y29"/>
     <mergeCell ref="Z28:Z29"/>
     <mergeCell ref="AA28:AA29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="K28:K29"/>
+    <mergeCell ref="L28:L29"/>
+    <mergeCell ref="M28:M29"/>
+    <mergeCell ref="N28:N29"/>
+    <mergeCell ref="O28:O29"/>
+    <mergeCell ref="P30:P31"/>
+    <mergeCell ref="Q30:Q31"/>
+    <mergeCell ref="R30:R31"/>
     <mergeCell ref="AB28:AB29"/>
     <mergeCell ref="AC28:AC29"/>
     <mergeCell ref="AD28:AD29"/>
@@ -4649,24 +4588,19 @@
     <mergeCell ref="S28:S29"/>
     <mergeCell ref="T28:T29"/>
     <mergeCell ref="U28:U29"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="K28:K29"/>
-    <mergeCell ref="L28:L29"/>
-    <mergeCell ref="M28:M29"/>
-    <mergeCell ref="N28:N29"/>
-    <mergeCell ref="O28:O29"/>
-    <mergeCell ref="P30:P31"/>
-    <mergeCell ref="Q30:Q31"/>
-    <mergeCell ref="R30:R31"/>
-    <mergeCell ref="S30:S31"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="K30:K31"/>
-    <mergeCell ref="L30:L31"/>
-    <mergeCell ref="M30:M31"/>
     <mergeCell ref="AF30:AF31"/>
     <mergeCell ref="AG30:AG31"/>
+    <mergeCell ref="AA30:AA31"/>
+    <mergeCell ref="AB30:AB31"/>
+    <mergeCell ref="AC30:AC31"/>
+    <mergeCell ref="AD30:AD31"/>
+    <mergeCell ref="AE30:AE31"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
     <mergeCell ref="A32:A33"/>
     <mergeCell ref="C32:C33"/>
     <mergeCell ref="D32:D33"/>
@@ -4676,11 +4610,6 @@
     <mergeCell ref="H32:H33"/>
     <mergeCell ref="I32:I33"/>
     <mergeCell ref="Z30:Z31"/>
-    <mergeCell ref="AA30:AA31"/>
-    <mergeCell ref="AB30:AB31"/>
-    <mergeCell ref="AC30:AC31"/>
-    <mergeCell ref="AD30:AD31"/>
-    <mergeCell ref="AE30:AE31"/>
     <mergeCell ref="T30:T31"/>
     <mergeCell ref="U30:U31"/>
     <mergeCell ref="V30:V31"/>
@@ -4689,6 +4618,13 @@
     <mergeCell ref="Y30:Y31"/>
     <mergeCell ref="N30:N31"/>
     <mergeCell ref="O30:O31"/>
+    <mergeCell ref="S30:S31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="L30:L31"/>
+    <mergeCell ref="M30:M31"/>
     <mergeCell ref="AE32:AE33"/>
     <mergeCell ref="AF32:AF33"/>
     <mergeCell ref="AG32:AG33"/>
@@ -4731,6 +4667,11 @@
     <mergeCell ref="M34:M35"/>
     <mergeCell ref="AF34:AF35"/>
     <mergeCell ref="AG34:AG35"/>
+    <mergeCell ref="AA34:AA35"/>
+    <mergeCell ref="AB34:AB35"/>
+    <mergeCell ref="AC34:AC35"/>
+    <mergeCell ref="AD34:AD35"/>
+    <mergeCell ref="AE34:AE35"/>
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="C36:C37"/>
     <mergeCell ref="D36:D37"/>
@@ -4740,11 +4681,6 @@
     <mergeCell ref="H36:H37"/>
     <mergeCell ref="I36:I37"/>
     <mergeCell ref="Z34:Z35"/>
-    <mergeCell ref="AA34:AA35"/>
-    <mergeCell ref="AB34:AB35"/>
-    <mergeCell ref="AC34:AC35"/>
-    <mergeCell ref="AD34:AD35"/>
-    <mergeCell ref="AE34:AE35"/>
     <mergeCell ref="T34:T35"/>
     <mergeCell ref="U34:U35"/>
     <mergeCell ref="V34:V35"/>
